--- a/data/S2012_13_FINAL.xlsx
+++ b/data/S2012_13_FINAL.xlsx
@@ -29,8 +29,11 @@
     <sheet name="SERIES" sheetId="20" state="visible" r:id="rId20"/>
     <sheet name="CLUBS" sheetId="21" state="visible" r:id="rId21"/>
     <sheet name="META" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet name="TODO" sheetId="23" state="visible" r:id="rId23"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="22" hidden="1">'TODO'!$A$1:$F$12</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -38,7 +41,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -53,8 +56,12 @@
       <name val="Arial"/>
       <b val="1"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -71,6 +78,11 @@
         <fgColor rgb="00E2EFDA"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00305496"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -84,11 +96,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -14775,7 +14793,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14910,6 +14928,153 @@
       <c r="E5" t="inlineStr">
         <is>
           <t>CLUB_S2012_13_0253</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id: CLUB_S2012_13_0235 'Spartak Pelhřimov B' prev→CLUB_S2011_12_0063 jen dle jména (město liší) — ověřit (D24)</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>[TBD] fate: CLUB_S2012_13_0031 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>[TBD] fate: CLUB_S2012_13_0033 fate nekonzist. ['sestup', 'setrval'] → 'sestup' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>[TBD] fate: CLUB_S2012_13_0217 fate nekonzist. ['postup', 'reorganizace'] → 'reorganizace' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>[TBD] fate: CLUB_S2012_13_0218 fate nekonzist. ['postup', 'reorganizace'] → 'reorganizace' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>[TBD] fate: CLUB_S2012_13_0222 fate nekonzist. ['setrval', 'setrval?'] → 'setrval' (cross-ref=ne) — ověřit</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>[TBD] fate: CLUB_S2012_13_0224 fate nekonzist. ['postup', 'reorganizace'] → 'reorganizace' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>[TBD] fate: CLUB_S2012_13_0225 fate nekonzist. ['postup', 'reorganizace'] → 'reorganizace' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>NODE_S2012_13_0021</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>[TBD] pyramida: SYSTEM NODE_S2012_13_0021 'Baráž o Extraligu' (L15, parent=NODE_S2012_13_0001) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>NODE_S2012_13_0028</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>[TBD] pyramida: SYSTEM NODE_S2012_13_0028 'Baráž o I.ligu' (L25, parent=NODE_S2012_13_0003) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>NODE_S2012_13_0045</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>[TBD] pyramida: SYSTEM NODE_S2012_13_0045 'O postup do I.ligy' (L15, parent=NODE_S2012_13_0039) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
         </is>
       </c>
     </row>
@@ -19222,8 +19387,6 @@
         </is>
       </c>
     </row>
-    <row r="102"/>
-    <row r="103"/>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
@@ -19303,7 +19466,6 @@
         </is>
       </c>
     </row>
-    <row r="111"/>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
@@ -35718,6 +35880,303 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="88" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>typ</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>reference</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>popis</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>vyřešeno? (ANO/ne)</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>poznámka kolegy</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>prev_club_id</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>CLUB_S2012_13_0235</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>CLUB_S2012_13_0235 'Spartak Pelhřimov B' prev→CLUB_S2011_12_0063 jen dle jména (město liší) — ověřit (D24)</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>fate</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>CLUB_S2012_13_0031</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>CLUB_S2012_13_0031 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>fate</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>CLUB_S2012_13_0033</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>CLUB_S2012_13_0033 fate nekonzist. ['sestup', 'setrval'] → 'sestup' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>fate</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>CLUB_S2012_13_0217</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>CLUB_S2012_13_0217 fate nekonzist. ['postup', 'reorganizace'] → 'reorganizace' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>fate</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>CLUB_S2012_13_0218</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>CLUB_S2012_13_0218 fate nekonzist. ['postup', 'reorganizace'] → 'reorganizace' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>fate</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>CLUB_S2012_13_0222</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>CLUB_S2012_13_0222 fate nekonzist. ['setrval', 'setrval?'] → 'setrval' (cross-ref=ne) — ověřit</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>fate</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>CLUB_S2012_13_0224</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>CLUB_S2012_13_0224 fate nekonzist. ['postup', 'reorganizace'] → 'reorganizace' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>fate</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>CLUB_S2012_13_0225</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>CLUB_S2012_13_0225 fate nekonzist. ['postup', 'reorganizace'] → 'reorganizace' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>pyramida</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>NODE_S2012_13_0021</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>SYSTEM NODE_S2012_13_0021 'Baráž o Extraligu' (L15, parent=NODE_S2012_13_0001) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>pyramida</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>NODE_S2012_13_0028</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>SYSTEM NODE_S2012_13_0028 'Baráž o I.ligu' (L25, parent=NODE_S2012_13_0003) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>pyramida</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>NODE_S2012_13_0045</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>SYSTEM NODE_S2012_13_0045 'O postup do I.ligy' (L15, parent=NODE_S2012_13_0039) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:F12"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/data/S2012_13_FINAL.xlsx
+++ b/data/S2012_13_FINAL.xlsx
@@ -32,7 +32,7 @@
     <sheet name="TODO" sheetId="23" state="visible" r:id="rId23"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="22" hidden="1">'TODO'!$A$1:$F$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="22" hidden="1">'TODO'!$A$1:$F$49</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -11811,6 +11811,11 @@
           <t>CLUB_S2011_12_0221</t>
         </is>
       </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>setrval</t>
+        </is>
+      </c>
       <c r="V4" t="inlineStr">
         <is>
           <t>TR_S2012_13_00314</t>
@@ -14793,7 +14798,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:E53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14934,7 +14939,7 @@
     <row r="6">
       <c r="C6" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id: CLUB_S2012_13_0235 'Spartak Pelhřimov B' prev→CLUB_S2011_12_0063 jen dle jména (město liší) — ověřit (D24)</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -14946,7 +14951,7 @@
     <row r="7">
       <c r="C7" t="inlineStr">
         <is>
-          <t>[TBD] fate: CLUB_S2012_13_0031 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -14958,7 +14963,7 @@
     <row r="8">
       <c r="C8" t="inlineStr">
         <is>
-          <t>[TBD] fate: CLUB_S2012_13_0033 fate nekonzist. ['sestup', 'setrval'] → 'sestup' (cross-ref=ano) — ověřit</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'KLH VT VTJ Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -14970,7 +14975,7 @@
     <row r="9">
       <c r="C9" t="inlineStr">
         <is>
-          <t>[TBD] fate: CLUB_S2012_13_0217 fate nekonzist. ['postup', 'reorganizace'] → 'reorganizace' (cross-ref=ano) — ověřit</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -14982,7 +14987,7 @@
     <row r="10">
       <c r="C10" t="inlineStr">
         <is>
-          <t>[TBD] fate: CLUB_S2012_13_0218 fate nekonzist. ['postup', 'reorganizace'] → 'reorganizace' (cross-ref=ano) — ověřit</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Sportovní klub Kadaň' → 'Kadaň' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -14994,7 +14999,7 @@
     <row r="11">
       <c r="C11" t="inlineStr">
         <is>
-          <t>[TBD] fate: CLUB_S2012_13_0222 fate nekonzist. ['setrval', 'setrval?'] → 'setrval' (cross-ref=ne) — ověřit</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -15006,7 +15011,7 @@
     <row r="12">
       <c r="C12" t="inlineStr">
         <is>
-          <t>[TBD] fate: CLUB_S2012_13_0224 fate nekonzist. ['postup', 'reorganizace'] → 'reorganizace' (cross-ref=ano) — ověřit</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'VSK Technika Brno' → 'Technika Brno' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -15018,7 +15023,7 @@
     <row r="13">
       <c r="C13" t="inlineStr">
         <is>
-          <t>[TBD] fate: CLUB_S2012_13_0225 fate nekonzist. ['postup', 'reorganizace'] → 'reorganizace' (cross-ref=ano) — ověřit</t>
+          <t>[TBD] prev_club_id / identita: TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -15028,14 +15033,9 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>NODE_S2012_13_0021</t>
-        </is>
-      </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>[TBD] pyramida: SYSTEM NODE_S2012_13_0021 'Baráž o Extraligu' (L15, parent=NODE_S2012_13_0001) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -15045,14 +15045,9 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>NODE_S2012_13_0028</t>
-        </is>
-      </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>[TBD] pyramida: SYSTEM NODE_S2012_13_0028 'Baráž o I.ligu' (L25, parent=NODE_S2012_13_0003) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Veselí nad Moravou' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -15062,17 +15057,471 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>NODE_S2012_13_0045</t>
-        </is>
-      </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>[TBD] pyramida: SYSTEM NODE_S2012_13_0045 'O postup do I.ligy' (L15, parent=NODE_S2012_13_0039) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'SHC Maso Brejcha Klatovy' → 'Klatovy' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vlci Jablonec nad Nisou' → 'Jablonec nad Nisou' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Chomutov' → 'SC Kolín' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'NED Hockey Nymburk' → 'Nymburk' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Plzeň' → 'Moravské Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'RT Torax Poruba' → 'Poruba' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'UHK LEV Slaný' → 'Slaný' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Veselí nad Moravou' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'SKP Rapid Plzeň' → 'Plzeň' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Ekonomické Stavby Plzeň' → 'Plzeň' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'IHT Brimstones Cheb' → 'Cheb' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'PSK 96 Cheb' → 'Cheb' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'BK JTC Nová Paka' → 'Nová Paka' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Stadion Nový Bydžov' → 'Nový Bydžov' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Závodní hokejové Pardubice' → 'Pardubice' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: K ověření, zda jde o B-tým nebo samostatný klub (Česká Třebová mohla mít dva různé kluby). Smart fix prev: 0650 (Sokol Česká Třebová = jiný klub) → 0656 (Perla II z 49/50 = B-tým Perly). Audit 04/2026.</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S2011_12_0063 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'HCM Warrior Brno' → 'Brno' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'RT Torax Poruba' → 'Poruba' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S2011_12_0067 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Havlíčkův Brod' → 'Rožnov pod Radhoštěm' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Havlíčkův Brod' → 'Rožnov pod Radhoštěm' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Havlíčkův Brod' → 'Rožnov pod Radhoštěm' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>NODE_S2012_13_0030</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>[TBD] pyramida (feeds_into): top-level kvalifikace bez feeds_into: 'KVAL  skupina A'</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>NODE_S2012_13_0031</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>[TBD] pyramida (feeds_into): top-level kvalifikace bez feeds_into: 'KVAL  skupina B'</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>NODE_S2012_13_0032</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>[TBD] pyramida (feeds_into): top-level kvalifikace bez feeds_into: 'KVAL  skupina C'</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
         <is>
           <t>TODO-auto</t>
         </is>
@@ -19387,6 +19836,8 @@
         </is>
       </c>
     </row>
+    <row r="102"/>
+    <row r="103"/>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
@@ -19417,6 +19868,11 @@
           <t>I.ČNHL (12 CZ) + SNHL (12 SVK)</t>
         </is>
       </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>NODE_S2012_13_0001</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -19429,6 +19885,11 @@
           <t>Kvalifikace o II.ligu</t>
         </is>
       </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>NODE_S2012_13_0003</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -19441,6 +19902,11 @@
           <t>Krajské přebory (nové velké kraje!)</t>
         </is>
       </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>NODE_S2012_13_0003</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -19453,6 +19919,11 @@
           <t>I.třída / I.B třída / Krajská soutěž</t>
         </is>
       </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>NODE_S2012_13_0039</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -19466,6 +19937,7 @@
         </is>
       </c>
     </row>
+    <row r="111"/>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
@@ -25426,12 +25898,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Třinec = TJ TŽ VŘSR Třinec (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj. **TŽ** = Třinecké železárny. **VŘSR** = Velka řijnova socialisticka revoluce (pojmenovani po vyroci VŘSR 1917). city Třinec.</t>
+          <t>Třinec = TJ TŽ VŘSR Třinec (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj. **TŽ** = Třinecké železárny. **VŘSR** = Velka řijnova socialisticka revoluce (pojmenovani po vyroci VŘSR 1917). city Třinec. || TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>TŽ VŘSR Třinec</t>
+          <t>Třinec</t>
         </is>
       </c>
     </row>
@@ -25594,12 +26066,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň.</t>
+          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň. || TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Plzeň</t>
+          <t>České Budějovice</t>
         </is>
       </c>
     </row>
@@ -25851,12 +26323,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Chomutov = KLH VT VTJ Chomutov (Wiki D42 - registr ustavy 04/2026). Severocesky/Ustecky kraj. **KLH VT VTJ** = post-revolucni nazev (KLH = klub lední hokej, VT = vrcholový tým, VTJ = Vojenská tělovýchovná jednota). city Chomutov.</t>
+          <t>Chomutov = KLH VT VTJ Chomutov (Wiki D42 - registr ustavy 04/2026). Severocesky/Ustecky kraj. **KLH VT VTJ** = post-revolucni nazev (KLH = klub lední hokej, VT = vrcholový tým, VTJ = Vojenská tělovýchovná jednota). city Chomutov. || TBD: city 'KLH VT VTJ Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>KLH VT VTJ Chomutov</t>
+          <t>Chomutov</t>
         </is>
       </c>
     </row>
@@ -25898,12 +26370,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov.</t>
+          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov. || TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Chomutov</t>
+          <t>Mladá Boleslav</t>
         </is>
       </c>
     </row>
@@ -26066,12 +26538,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Kadaň = Sportovní klub Kadaň (Wiki D42 - registr ustavy 04/2026). Severocesky/Ustecky kraj (okres Chomutov). city Kadaň.</t>
+          <t>Kadaň = Sportovní klub Kadaň (Wiki D42 - registr ustavy 04/2026). Severocesky/Ustecky kraj (okres Chomutov). city Kadaň. || TBD: city 'Sportovní klub Kadaň' → 'Kadaň' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Sportovní klub Kadaň</t>
+          <t>Kadaň</t>
         </is>
       </c>
     </row>
@@ -26150,12 +26622,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov.</t>
+          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov. || TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Hradec Králové</t>
         </is>
       </c>
     </row>
@@ -26528,12 +27000,12 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Brno = VSK Technika Brno (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj. **VSK Technika** = Vysokoškolský sportovní klub (VUT Brno). city Brno.</t>
+          <t>Brno = VSK Technika Brno (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj. **VSK Technika** = Vysokoškolský sportovní klub (VUT Brno). city Brno. || TBD: city 'VSK Technika Brno' → 'Technika Brno' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>VSK Technika Brno</t>
+          <t>Technika Brno</t>
         </is>
       </c>
     </row>
@@ -26792,12 +27264,12 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Veselí nad Moravou = TJ Lokomotiva Veselí nad Moravou (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Hodonín). Železničárský klub. NE Veselí nad Lužnicí (Jihocesky). city Veselí nad Moravou.</t>
+          <t>Veselí nad Moravou = TJ Lokomotiva Veselí nad Moravou (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Hodonín). Železničárský klub. NE Veselí nad Lužnicí (Jihocesky). city Veselí nad Moravou. || TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach] || TBD: city 'Veselí nad Moravou' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Lokomotiva  Veselí nad Moravou</t>
+          <t>Veselí nad Lužnicí</t>
         </is>
       </c>
     </row>
@@ -27516,12 +27988,12 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>Klatovy = SHC Maso Brejcha Klatovy (Wiki D42 - registr ustavy 04/2026). Plzensky kraj. **Maso Brejcha** = sponzor (řeznictví). city Klatovy.</t>
+          <t>Klatovy = SHC Maso Brejcha Klatovy (Wiki D42 - registr ustavy 04/2026). Plzensky kraj. **Maso Brejcha** = sponzor (řeznictví). city Klatovy. || TBD: city 'SHC Maso Brejcha Klatovy' → 'Klatovy' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>SHC Maso Brejcha Klatovy</t>
+          <t>Klatovy</t>
         </is>
       </c>
     </row>
@@ -27558,12 +28030,12 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Klášterec nad Ohří = Sokol Klášterec (Wiki D42 - registr ustavy 04/2026). Severocesky kraj (okres Chomutov). HC Klášterec dnes mensi soutez. city Klášterec nad Ohří.</t>
+          <t>Klášterec nad Ohří = Sokol Klášterec (Wiki D42 - registr ustavy 04/2026). Severocesky kraj (okres Chomutov). HC Klášterec dnes mensi soutez. city Klášterec nad Ohří. || TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>Klášterec</t>
+          <t>Klášterec nad Ohří</t>
         </is>
       </c>
     </row>
@@ -27684,12 +28156,12 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>Jablonec nad Nisou = HC Vlci Jablonec nL Nisou (Wiki D42 - registr ustavy 04/2026). Severocesky/Liberecky kraj. city Jablonec nad Nisou.</t>
+          <t>Jablonec nad Nisou = HC Vlci Jablonec nL Nisou (Wiki D42 - registr ustavy 04/2026). Severocesky/Liberecky kraj. city Jablonec nad Nisou. || TBD: city 'Vlci Jablonec nad Nisou' → 'Jablonec nad Nisou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>Vlci Jablonec nad Nisou</t>
+          <t>Jablonec nad Nisou</t>
         </is>
       </c>
     </row>
@@ -27894,12 +28366,12 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov.</t>
+          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov. || TBD: city 'Chomutov' → 'SC Kolín' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>Chomutov</t>
+          <t>SC Kolín</t>
         </is>
       </c>
     </row>
@@ -27936,12 +28408,12 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>Nymburk = NED Hockey Nymburk (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj. Post-revolucni. city Nymburk.</t>
+          <t>Nymburk = NED Hockey Nymburk (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj. Post-revolucni. city Nymburk. || TBD: city 'NED Hockey Nymburk' → 'Nymburk' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>NED Hockey Nymburk</t>
+          <t>Nymburk</t>
         </is>
       </c>
     </row>
@@ -28013,14 +28485,9 @@
           <t>L30</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>CLUB_S2011_12_0015</t>
-        </is>
-      </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>B-tým Slavoj OKP Roudnice. city ✓. || Roudnice nL Labem = HC Roudnice nL Labem (Wiki + eliteprospects + hcroudnice.cz - registr ustavy 04/2026). KLUB ZALOZEN 28.8.1931 v restauraci U Vagneru jako 'HOCKEY CLUB Roudnice n.L.' - jeden z nejstarsich v Severocesku! Genealogie: HC Roudnice nL (1931-1949) -&gt; TJ Sokol Benzina Roudnice (1949+, podnik Benzina = palivovy podnik) -&gt; TJ Spartak Roudnice (1951+ DSO) -&gt; HC Roudnice (1993, samostatny po ~44 letech!). MILNIK: 2007/08 do 2.ligy, 2009/10 sestup do KP, 2011 prodali licenci do Poruby. Dnes Ústecká krajska liga + uspesny zensky tym (Patterns: Sokol Benzina Roudnice, Spartak Roudnice, HC Roudnice. city Roudnice nad Labem.</t>
+          <t>B-tým Slavoj OKP Roudnice. city ✓. || Roudnice nL Labem = HC Roudnice nL Labem (Wiki + eliteprospects + hcroudnice.cz - registr ustavy 04/2026). KLUB ZALOZEN 28.8.1931 v restauraci U Vagneru jako 'HOCKEY CLUB Roudnice n.L.' - jeden z nejstarsich v Severocesku! Genealogie: HC Roudnice nL (1931-1949) -&gt; TJ Sokol Benzina Roudnice (1949+, podnik Benzina = palivovy podnik) -&gt; TJ Spartak Roudnice (1951+ DSO) -&gt; HC Roudnice (1993, samostatny po ~44 letech!). MILNIK: 2007/08 do 2.ligy, 2009/10 sestup do KP, 2011 prodali licenci do Poruby. Dnes Ústecká krajska liga + uspesny zensky tym (Patterns: Sokol Benzina Roudnice, Spartak Roudnice, HC Roudnice. city Roudnice nad Labem. || TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -28067,12 +28534,12 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň.</t>
+          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň. || TBD: city 'Plzeň' → 'Moravské Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>Plzeň</t>
+          <t>Moravské Budějovice</t>
         </is>
       </c>
     </row>
@@ -28109,12 +28576,12 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>Slovan JH = HC Vajgar/Strelci JH (Wiki D42 - registr ustavy 04/2026). Chain VBK Vajgar (1929). NE Hradec Kralove. city Jindřichův Hradec.</t>
+          <t>Slovan JH = HC Vajgar/Strelci JH (Wiki D42 - registr ustavy 04/2026). Chain VBK Vajgar (1929). NE Hradec Kralove. city Jindřichův Hradec. || TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>Vajgar Jindřichův Hradec</t>
+          <t>Jindřichův Hradec</t>
         </is>
       </c>
     </row>
@@ -28144,14 +28611,9 @@
           <t>L30</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>CLUB_S2011_12_0015</t>
-        </is>
-      </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>B-tým Slavoj OKP Roudnice. city ✓. || Roudnice nL Labem = HC Roudnice nL Labem (Wiki + eliteprospects + hcroudnice.cz - registr ustavy 04/2026). KLUB ZALOZEN 28.8.1931 v restauraci U Vagneru jako 'HOCKEY CLUB Roudnice n.L.' - jeden z nejstarsich v Severocesku! Genealogie: HC Roudnice nL (1931-1949) -&gt; TJ Sokol Benzina Roudnice (1949+, podnik Benzina = palivovy podnik) -&gt; TJ Spartak Roudnice (1951+ DSO) -&gt; HC Roudnice (1993, samostatny po ~44 letech!). MILNIK: 2007/08 do 2.ligy, 2009/10 sestup do KP, 2011 prodali licenci do Poruby. Dnes Ústecká krajska liga + uspesny zensky tym (Patterns: Sokol Benzina Roudnice, Spartak Roudnice, HC Roudnice. city Roudnice nad Labem.</t>
+          <t>B-tým Slavoj OKP Roudnice. city ✓. || Roudnice nL Labem = HC Roudnice nL Labem (Wiki + eliteprospects + hcroudnice.cz - registr ustavy 04/2026). KLUB ZALOZEN 28.8.1931 v restauraci U Vagneru jako 'HOCKEY CLUB Roudnice n.L.' - jeden z nejstarsich v Severocesku! Genealogie: HC Roudnice nL (1931-1949) -&gt; TJ Sokol Benzina Roudnice (1949+, podnik Benzina = palivovy podnik) -&gt; TJ Spartak Roudnice (1951+ DSO) -&gt; HC Roudnice (1993, samostatny po ~44 letech!). MILNIK: 2007/08 do 2.ligy, 2009/10 sestup do KP, 2011 prodali licenci do Poruby. Dnes Ústecká krajska liga + uspesny zensky tym (Patterns: Sokol Benzina Roudnice, Spartak Roudnice, HC Roudnice. city Roudnice nad Labem. || TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -28277,12 +28739,12 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>Ostrava (Poruba) = HC RT Torax Poruba (Wiki D42 - registr ustavy 04/2026). Moravskoslezsky kraj. **RT Torax** = sponzor (medical device firma). Patterns: HK Poruba. city Ostrava (Poruba).</t>
+          <t>Ostrava (Poruba) = HC RT Torax Poruba (Wiki D42 - registr ustavy 04/2026). Moravskoslezsky kraj. **RT Torax** = sponzor (medical device firma). Patterns: HK Poruba. city Ostrava (Poruba). || TBD: city 'RT Torax Poruba' → 'Poruba' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>RT Torax Poruba</t>
+          <t>Poruba</t>
         </is>
       </c>
     </row>
@@ -28613,12 +29075,12 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov.</t>
+          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov. || TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>Chomutov</t>
+          <t>Mladá Boleslav</t>
         </is>
       </c>
     </row>
@@ -28786,12 +29248,12 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>Slaný = UHK LEV Slaný (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj (okres Kladno). **UHK** = Univerzitni hokejovy klub. Patterns: HK Lev Slaný. city Slaný.</t>
+          <t>Slaný = UHK LEV Slaný (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj (okres Kladno). **UHK** = Univerzitni hokejovy klub. Patterns: HK Lev Slaný. city Slaný. || TBD: city 'UHK LEV Slaný' → 'Slaný' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>UHK LEV Slaný</t>
+          <t>Slaný</t>
         </is>
       </c>
     </row>
@@ -28910,14 +29372,9 @@
           <t>L40</t>
         </is>
       </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>CLUB_S2011_12_0015</t>
-        </is>
-      </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>B-tým Slavoj OKP Roudnice. city ✓. || Roudnice nL Labem = HC Roudnice nL Labem (Wiki + eliteprospects + hcroudnice.cz - registr ustavy 04/2026). KLUB ZALOZEN 28.8.1931 v restauraci U Vagneru jako 'HOCKEY CLUB Roudnice n.L.' - jeden z nejstarsich v Severocesku! Genealogie: HC Roudnice nL (1931-1949) -&gt; TJ Sokol Benzina Roudnice (1949+, podnik Benzina = palivovy podnik) -&gt; TJ Spartak Roudnice (1951+ DSO) -&gt; HC Roudnice (1993, samostatny po ~44 letech!). MILNIK: 2007/08 do 2.ligy, 2009/10 sestup do KP, 2011 prodali licenci do Poruby. Dnes Ústecká krajska liga + uspesny zensky tym (Patterns: Sokol Benzina Roudnice, Spartak Roudnice, HC Roudnice. city Roudnice nad Labem.</t>
+          <t>B-tým Slavoj OKP Roudnice. city ✓. || Roudnice nL Labem = HC Roudnice nL Labem (Wiki + eliteprospects + hcroudnice.cz - registr ustavy 04/2026). KLUB ZALOZEN 28.8.1931 v restauraci U Vagneru jako 'HOCKEY CLUB Roudnice n.L.' - jeden z nejstarsich v Severocesku! Genealogie: HC Roudnice nL (1931-1949) -&gt; TJ Sokol Benzina Roudnice (1949+, podnik Benzina = palivovy podnik) -&gt; TJ Spartak Roudnice (1951+ DSO) -&gt; HC Roudnice (1993, samostatny po ~44 letech!). MILNIK: 2007/08 do 2.ligy, 2009/10 sestup do KP, 2011 prodali licenci do Poruby. Dnes Ústecká krajska liga + uspesny zensky tym (Patterns: Sokol Benzina Roudnice, Spartak Roudnice, HC Roudnice. city Roudnice nad Labem. || TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
@@ -29431,12 +29888,12 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň.</t>
+          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň. || TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>Plzeň</t>
+          <t>České Budějovice</t>
         </is>
       </c>
     </row>
@@ -29520,12 +29977,12 @@
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>Veselí nad Moravou = TJ Lokomotiva Veselí nad Moravou (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Hodonín). Železničárský klub. NE Veselí nad Lužnicí (Jihocesky). city Veselí nad Moravou.</t>
+          <t>Veselí nad Moravou = TJ Lokomotiva Veselí nad Moravou (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Hodonín). Železničárský klub. NE Veselí nad Lužnicí (Jihocesky). city Veselí nad Moravou. || TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach] || TBD: city 'Veselí nad Moravou' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>Lokomotiva  Veselí nad Moravou</t>
+          <t>Veselí nad Lužnicí</t>
         </is>
       </c>
     </row>
@@ -29903,12 +30360,12 @@
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>Slovan JH = HC Vajgar/Strelci JH (Wiki D42 - registr ustavy 04/2026). Chain VBK Vajgar (1929). NE Hradec Kralove. city Jindřichův Hradec.</t>
+          <t>Slovan JH = HC Vajgar/Strelci JH (Wiki D42 - registr ustavy 04/2026). Chain VBK Vajgar (1929). NE Hradec Kralove. city Jindřichův Hradec. || TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>Vajgar Jindřichův Hradec</t>
+          <t>Jindřichův Hradec</t>
         </is>
       </c>
     </row>
@@ -31173,12 +31630,12 @@
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>Plzeň = SKP Rapid Plzeň (Wiki D42 - registr ustavy 04/2026). Plzensky kraj. **SKP** = Sportovni klub policie. city Plzeň.</t>
+          <t>Plzeň = SKP Rapid Plzeň (Wiki D42 - registr ustavy 04/2026). Plzensky kraj. **SKP** = Sportovni klub policie. city Plzeň. || TBD: city 'SKP Rapid Plzeň' → 'Plzeň' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t>SKP Rapid Plzeň</t>
+          <t>Plzeň</t>
         </is>
       </c>
     </row>
@@ -31524,12 +31981,12 @@
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>Plzeň = HC Ekonomické Stavby Plzeň (Wiki D42 - registr ustavy 04/2026). Plzensky kraj. city Plzeň.</t>
+          <t>Plzeň = HC Ekonomické Stavby Plzeň (Wiki D42 - registr ustavy 04/2026). Plzensky kraj. city Plzeň. || TBD: city 'Ekonomické Stavby Plzeň' → 'Plzeň' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t>Ekonomické Stavby Plzeň</t>
+          <t>Plzeň</t>
         </is>
       </c>
     </row>
@@ -32923,12 +33380,12 @@
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t>Cheb = IHT Brimstones Cheb (Wiki D42 - registr ustavy 04/2026). Karlovarsky kraj. Post-revolucni anglicky nazev. city Cheb.</t>
+          <t>Cheb = IHT Brimstones Cheb (Wiki D42 - registr ustavy 04/2026). Karlovarsky kraj. Post-revolucni anglicky nazev. city Cheb. || TBD: city 'IHT Brimstones Cheb' → 'Cheb' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J181" t="inlineStr">
         <is>
-          <t>IHT Brimstones Cheb</t>
+          <t>Cheb</t>
         </is>
       </c>
     </row>
@@ -33007,12 +33464,12 @@
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t>Cheb = PSK 96 Cheb (Wiki D42 - registr ustavy 04/2026). Karlovarsky kraj. **PSK 96** = Policejni sportovni klub zalozen 1996. city Cheb.</t>
+          <t>Cheb = PSK 96 Cheb (Wiki D42 - registr ustavy 04/2026). Karlovarsky kraj. **PSK 96** = Policejni sportovni klub zalozen 1996. city Cheb. || TBD: city 'PSK 96 Cheb' → 'Cheb' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J183" t="inlineStr">
         <is>
-          <t>PSK 96 Cheb</t>
+          <t>Cheb</t>
         </is>
       </c>
     </row>
@@ -33595,12 +34052,12 @@
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t>Nová Paka = BK JTC Nová Paka (Wiki D42 - registr ustavy 04/2026). Vychodocesky/Kralovehradecky kraj (okres Jicin). **BK JTC** = Bruslarsky klub Jicinske telovychovne centrum. city Nová Paka.</t>
+          <t>Nová Paka = BK JTC Nová Paka (Wiki D42 - registr ustavy 04/2026). Vychodocesky/Kralovehradecky kraj (okres Jicin). **BK JTC** = Bruslarsky klub Jicinske telovychovne centrum. city Nová Paka. || TBD: city 'BK JTC Nová Paka' → 'Nová Paka' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J197" t="inlineStr">
         <is>
-          <t>BK JTC Nová Paka</t>
+          <t>Nová Paka</t>
         </is>
       </c>
     </row>
@@ -33679,12 +34136,12 @@
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t>Nový Bydžov = TJ Stadion Nový Bydžov (Wiki D42 - registr ustavy 04/2026). Vychodocesky/Kralovehradecky kraj. Patterns: OSP Nový Bydžov. city Nový Bydžov.</t>
+          <t>Nový Bydžov = TJ Stadion Nový Bydžov (Wiki D42 - registr ustavy 04/2026). Vychodocesky/Kralovehradecky kraj. Patterns: OSP Nový Bydžov. city Nový Bydžov. || TBD: city 'Stadion Nový Bydžov' → 'Nový Bydžov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J199" t="inlineStr">
         <is>
-          <t>Stadion Nový Bydžov</t>
+          <t>Nový Bydžov</t>
         </is>
       </c>
     </row>
@@ -34057,12 +34514,12 @@
       </c>
       <c r="I208" t="inlineStr">
         <is>
-          <t>Pardubice = HC Závodní hokejové Pardubice (Wiki D42 - registr ustavy 04/2026). Pardubicky kraj. **Závodní hokejová liga**. city Pardubice.</t>
+          <t>Pardubice = HC Závodní hokejové Pardubice (Wiki D42 - registr ustavy 04/2026). Pardubicky kraj. **Závodní hokejová liga**. city Pardubice. || TBD: city 'Závodní hokejové Pardubice' → 'Pardubice' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J208" t="inlineStr">
         <is>
-          <t>Závodní hokejové Pardubice</t>
+          <t>Pardubice</t>
         </is>
       </c>
     </row>
@@ -34734,12 +35191,12 @@
       </c>
       <c r="I224" t="inlineStr">
         <is>
-          <t>Brno = HCM Warrior Brno (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj. **HCM** = post-revolucni klub. city Brno.</t>
+          <t>Brno = HCM Warrior Brno (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj. **HCM** = post-revolucni klub. city Brno. || TBD: city 'HCM Warrior Brno' → 'Brno' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J224" t="inlineStr">
         <is>
-          <t>HCM Warrior Brno</t>
+          <t>Brno</t>
         </is>
       </c>
     </row>
@@ -35332,12 +35789,12 @@
       </c>
       <c r="I238" t="inlineStr">
         <is>
-          <t>Ostrava (Poruba) = HC RT Torax Poruba (Wiki D42 - registr ustavy 04/2026). Moravskoslezsky kraj. **RT Torax** = sponzor (medical device firma). Patterns: HK Poruba. city Ostrava (Poruba).</t>
+          <t>Ostrava (Poruba) = HC RT Torax Poruba (Wiki D42 - registr ustavy 04/2026). Moravskoslezsky kraj. **RT Torax** = sponzor (medical device firma). Patterns: HK Poruba. city Ostrava (Poruba). || TBD: city 'RT Torax Poruba' → 'Poruba' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J238" t="inlineStr">
         <is>
-          <t>RT Torax Poruba</t>
+          <t>Poruba</t>
         </is>
       </c>
     </row>
@@ -35463,12 +35920,12 @@
       </c>
       <c r="I241" t="inlineStr">
         <is>
-          <t>Jiskra Havlíčkův Brod = HC Rebel HB (Wiki D42 - registr ustavy 04/2026). city Havlíčkův Brod.</t>
+          <t>Jiskra Havlíčkův Brod = HC Rebel HB (Wiki D42 - registr ustavy 04/2026). city Havlíčkův Brod. || TBD: city 'Havlíčkův Brod' → 'Rožnov pod Radhoštěm' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J241" t="inlineStr">
         <is>
-          <t>Havlíčkův Brod</t>
+          <t>Rožnov pod Radhoštěm</t>
         </is>
       </c>
     </row>
@@ -35552,12 +36009,12 @@
       </c>
       <c r="I243" t="inlineStr">
         <is>
-          <t>Jiskra Havlíčkův Brod = HC Rebel HB (Wiki D42 - registr ustavy 04/2026). city Havlíčkův Brod.</t>
+          <t>Jiskra Havlíčkův Brod = HC Rebel HB (Wiki D42 - registr ustavy 04/2026). city Havlíčkův Brod. || TBD: city 'Havlíčkův Brod' → 'Rožnov pod Radhoštěm' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J243" t="inlineStr">
         <is>
-          <t>Havlíčkův Brod</t>
+          <t>Rožnov pod Radhoštěm</t>
         </is>
       </c>
     </row>
@@ -35636,12 +36093,12 @@
       </c>
       <c r="I245" t="inlineStr">
         <is>
-          <t>Jiskra Havlíčkův Brod = HC Rebel HB (Wiki D42 - registr ustavy 04/2026). city Havlíčkův Brod.</t>
+          <t>Jiskra Havlíčkův Brod = HC Rebel HB (Wiki D42 - registr ustavy 04/2026). city Havlíčkův Brod. || TBD: city 'Havlíčkův Brod' → 'Rožnov pod Radhoštěm' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J245" t="inlineStr">
         <is>
-          <t>Havlíčkův Brod</t>
+          <t>Rožnov pod Radhoštěm</t>
         </is>
       </c>
     </row>
@@ -35886,11 +36343,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
     <col width="26" customWidth="1" min="3" max="3"/>
     <col width="88" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
@@ -35935,21 +36392,19 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>prev_club_id</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>CLUB_S2012_13_0235</t>
+          <t>CLUB_S2012_13_0004</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>CLUB_S2012_13_0235 'Spartak Pelhřimov B' prev→CLUB_S2011_12_0063 jen dle jména (město liší) — ověřit (D24)</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
+          <t>TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -35957,21 +36412,19 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>fate</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>CLUB_S2012_13_0031</t>
+          <t>CLUB_S2012_13_0008</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>CLUB_S2012_13_0031 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
+          <t>TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -35979,21 +36432,19 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>fate</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>CLUB_S2012_13_0033</t>
+          <t>CLUB_S2012_13_0014</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>CLUB_S2012_13_0033 fate nekonzist. ['sestup', 'setrval'] → 'sestup' (cross-ref=ano) — ověřit</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
+          <t>TBD: city 'KLH VT VTJ Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -36001,21 +36452,19 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>fate</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>CLUB_S2012_13_0217</t>
+          <t>CLUB_S2012_13_0015</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>CLUB_S2012_13_0217 fate nekonzist. ['postup', 'reorganizace'] → 'reorganizace' (cross-ref=ano) — ověřit</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
+          <t>TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -36023,21 +36472,19 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>fate</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>CLUB_S2012_13_0218</t>
+          <t>CLUB_S2012_13_0021</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>CLUB_S2012_13_0218 fate nekonzist. ['postup', 'reorganizace'] → 'reorganizace' (cross-ref=ano) — ověřit</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
+          <t>TBD: city 'Sportovní klub Kadaň' → 'Kadaň' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -36045,21 +36492,19 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>fate</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>CLUB_S2012_13_0222</t>
+          <t>CLUB_S2012_13_0023</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>CLUB_S2012_13_0222 fate nekonzist. ['setrval', 'setrval?'] → 'setrval' (cross-ref=ne) — ověřit</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
+          <t>TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -36067,21 +36512,19 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>fate</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>CLUB_S2012_13_0224</t>
+          <t>CLUB_S2012_13_0032</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>CLUB_S2012_13_0224 fate nekonzist. ['postup', 'reorganizace'] → 'reorganizace' (cross-ref=ano) — ověřit</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
+          <t>TBD: city 'VSK Technika Brno' → 'Technika Brno' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -36089,21 +36532,19 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>fate</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>CLUB_S2012_13_0225</t>
+          <t>CLUB_S2012_13_0035</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>CLUB_S2012_13_0225 fate nekonzist. ['postup', 'reorganizace'] → 'reorganizace' (cross-ref=ano) — ověřit</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
+          <t>TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -36111,21 +36552,19 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>pyramida</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>NODE_S2012_13_0021</t>
+          <t>CLUB_S2012_13_0039</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>SYSTEM NODE_S2012_13_0021 'Baráž o Extraligu' (L15, parent=NODE_S2012_13_0001) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
+          <t>TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -36133,21 +36572,19 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>pyramida</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>NODE_S2012_13_0028</t>
+          <t>CLUB_S2012_13_0039</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>SYSTEM NODE_S2012_13_0028 'Baráž o I.ligu' (L25, parent=NODE_S2012_13_0003) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
+          <t>TBD: city 'Veselí nad Moravou' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -36155,24 +36592,762 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>pyramida</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>NODE_S2012_13_0045</t>
+          <t>CLUB_S2012_13_0057</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>SYSTEM NODE_S2012_13_0045 'O postup do I.ligy' (L15, parent=NODE_S2012_13_0039) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
+          <t>TBD: city 'SHC Maso Brejcha Klatovy' → 'Klatovy' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>CLUB_S2012_13_0058</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>CLUB_S2012_13_0061</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>TBD: city 'Vlci Jablonec nad Nisou' → 'Jablonec nad Nisou' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>CLUB_S2012_13_0067</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>TBD: city 'Chomutov' → 'SC Kolín' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>CLUB_S2012_13_0068</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>TBD: city 'NED Hockey Nymburk' → 'Nymburk' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>CLUB_S2012_13_0070</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>CLUB_S2012_13_0071</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>TBD: city 'Plzeň' → 'Moravské Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>CLUB_S2012_13_0072</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>CLUB_S2012_13_0073</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>CLUB_S2012_13_0077</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>TBD: city 'RT Torax Poruba' → 'Poruba' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>CLUB_S2012_13_0085</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>CLUB_S2012_13_0089</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>TBD: city 'UHK LEV Slaný' → 'Slaný' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>CLUB_S2012_13_0092</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="inlineStr">
+        <is>
+          <t>TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>CLUB_S2012_13_0105</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>CLUB_S2012_13_0107</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="inlineStr">
+        <is>
+          <t>TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>CLUB_S2012_13_0107</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>TBD: city 'Veselí nad Moravou' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>CLUB_S2012_13_0116</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="inlineStr">
+        <is>
+          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>CLUB_S2012_13_0148</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>TBD: city 'SKP Rapid Plzeň' → 'Plzeň' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>CLUB_S2012_13_0156</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="inlineStr">
+        <is>
+          <t>TBD: city 'Ekonomické Stavby Plzeň' → 'Plzeň' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>CLUB_S2012_13_0175</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="inlineStr">
+        <is>
+          <t>TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>CLUB_S2012_13_0189</t>
+        </is>
+      </c>
+      <c r="D32" s="5" t="inlineStr">
+        <is>
+          <t>TBD: city 'IHT Brimstones Cheb' → 'Cheb' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>CLUB_S2012_13_0191</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="inlineStr">
+        <is>
+          <t>TBD: city 'PSK 96 Cheb' → 'Cheb' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>CLUB_S2012_13_0205</t>
+        </is>
+      </c>
+      <c r="D34" s="5" t="inlineStr">
+        <is>
+          <t>TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>CLUB_S2012_13_0206</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="inlineStr">
+        <is>
+          <t>TBD: city 'BK JTC Nová Paka' → 'Nová Paka' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>CLUB_S2012_13_0208</t>
+        </is>
+      </c>
+      <c r="D36" s="5" t="inlineStr">
+        <is>
+          <t>TBD: city 'Stadion Nový Bydžov' → 'Nový Bydžov' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>CLUB_S2012_13_0221</t>
+        </is>
+      </c>
+      <c r="D37" s="5" t="inlineStr">
+        <is>
+          <t>TBD: city 'Závodní hokejové Pardubice' → 'Pardubice' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>CLUB_S2012_13_0222</t>
+        </is>
+      </c>
+      <c r="D38" s="5" t="inlineStr">
+        <is>
+          <t>TBD: K ověření, zda jde o B-tým nebo samostatný klub (Česká Třebová mohla mít dva různé kluby). Smart fix prev: 0650 (Sokol Česká Třebová = jiný klub) → 0656 (Perla II z 49/50 = B-tým Perly). Audit 04/2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>CLUB_S2012_13_0223</t>
+        </is>
+      </c>
+      <c r="D39" s="5" t="inlineStr">
+        <is>
+          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>CLUB_S2012_13_0235</t>
+        </is>
+      </c>
+      <c r="D40" s="5" t="inlineStr">
+        <is>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S2011_12_0063 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>CLUB_S2012_13_0243</t>
+        </is>
+      </c>
+      <c r="D41" s="5" t="inlineStr">
+        <is>
+          <t>TBD: city 'HCM Warrior Brno' → 'Brno' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>CLUB_S2012_13_0259</t>
+        </is>
+      </c>
+      <c r="D42" s="5" t="inlineStr">
+        <is>
+          <t>TBD: city 'RT Torax Poruba' → 'Poruba' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>CLUB_S2012_13_0261</t>
+        </is>
+      </c>
+      <c r="D43" s="5" t="inlineStr">
+        <is>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S2011_12_0067 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>CLUB_S2012_13_0262</t>
+        </is>
+      </c>
+      <c r="D44" s="5" t="inlineStr">
+        <is>
+          <t>TBD: city 'Havlíčkův Brod' → 'Rožnov pod Radhoštěm' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>CLUB_S2012_13_0264</t>
+        </is>
+      </c>
+      <c r="D45" s="5" t="inlineStr">
+        <is>
+          <t>TBD: city 'Havlíčkův Brod' → 'Rožnov pod Radhoštěm' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>CLUB_S2012_13_0266</t>
+        </is>
+      </c>
+      <c r="D46" s="5" t="inlineStr">
+        <is>
+          <t>TBD: city 'Havlíčkův Brod' → 'Rožnov pod Radhoštěm' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>pyramida (feeds_into)</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>NODE_S2012_13_0030</t>
+        </is>
+      </c>
+      <c r="D47" s="5" t="inlineStr">
+        <is>
+          <t>top-level kvalifikace bez feeds_into: 'KVAL  skupina A'</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>pyramida (feeds_into)</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>NODE_S2012_13_0031</t>
+        </is>
+      </c>
+      <c r="D48" s="5" t="inlineStr">
+        <is>
+          <t>top-level kvalifikace bez feeds_into: 'KVAL  skupina B'</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>pyramida (feeds_into)</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>NODE_S2012_13_0032</t>
+        </is>
+      </c>
+      <c r="D49" s="5" t="inlineStr">
+        <is>
+          <t>top-level kvalifikace bez feeds_into: 'KVAL  skupina C'</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F12"/>
+  <autoFilter ref="A1:F49"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -38113,11 +39288,6 @@
           <t>CLUB_S2012_13_0070</t>
         </is>
       </c>
-      <c r="R31" t="inlineStr">
-        <is>
-          <t>CLUB_S2011_12_0015</t>
-        </is>
-      </c>
       <c r="U31" t="inlineStr">
         <is>
           <t>setrval</t>
@@ -38350,11 +39520,6 @@
       <c r="Q34" t="inlineStr">
         <is>
           <t>CLUB_S2012_13_0073</t>
-        </is>
-      </c>
-      <c r="R34" t="inlineStr">
-        <is>
-          <t>CLUB_S2011_12_0015</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
@@ -43907,11 +45072,6 @@
           <t>CLUB_S2012_13_0092</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>CLUB_S2011_12_0015</t>
-        </is>
-      </c>
       <c r="U12" t="inlineStr">
         <is>
           <t>reorganizace</t>
@@ -44217,11 +45377,6 @@
       <c r="Q16" t="inlineStr">
         <is>
           <t>CLUB_S2012_13_0092</t>
-        </is>
-      </c>
-      <c r="R16" t="inlineStr">
-        <is>
-          <t>CLUB_S2011_12_0015</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">

--- a/data/S2012_13_FINAL.xlsx
+++ b/data/S2012_13_FINAL.xlsx
@@ -32,7 +32,7 @@
     <sheet name="TODO" sheetId="23" state="visible" r:id="rId23"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="22" hidden="1">'TODO'!$A$1:$F$49</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="22" hidden="1">'TODO'!$A$1:$F$37</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -14798,7 +14798,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E53"/>
+  <dimension ref="A1:E41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14951,7 +14951,7 @@
     <row r="7">
       <c r="C7" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'KLH VT VTJ Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -14963,7 +14963,7 @@
     <row r="8">
       <c r="C8" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'KLH VT VTJ Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Sportovní klub Kadaň' → 'Kadaň' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -14975,7 +14975,7 @@
     <row r="9">
       <c r="C9" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'VSK Technika Brno' → 'Technika Brno' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -14987,7 +14987,7 @@
     <row r="10">
       <c r="C10" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Sportovní klub Kadaň' → 'Kadaň' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -14999,7 +14999,7 @@
     <row r="11">
       <c r="C11" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -15011,7 +15011,7 @@
     <row r="12">
       <c r="C12" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'VSK Technika Brno' → 'Technika Brno' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'SHC Maso Brejcha Klatovy' → 'Klatovy' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -15023,7 +15023,7 @@
     <row r="13">
       <c r="C13" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -15035,7 +15035,7 @@
     <row r="14">
       <c r="C14" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vlci Jablonec nad Nisou' → 'Jablonec nad Nisou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -15047,7 +15047,7 @@
     <row r="15">
       <c r="C15" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Veselí nad Moravou' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'NED Hockey Nymburk' → 'Nymburk' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -15059,7 +15059,7 @@
     <row r="16">
       <c r="C16" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'SHC Maso Brejcha Klatovy' → 'Klatovy' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -15071,7 +15071,7 @@
     <row r="17">
       <c r="C17" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -15083,7 +15083,7 @@
     <row r="18">
       <c r="C18" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Vlci Jablonec nad Nisou' → 'Jablonec nad Nisou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -15095,7 +15095,7 @@
     <row r="19">
       <c r="C19" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Chomutov' → 'SC Kolín' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'RT Torax Poruba' → 'Poruba' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -15107,7 +15107,7 @@
     <row r="20">
       <c r="C20" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'NED Hockey Nymburk' → 'Nymburk' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'UHK LEV Slaný' → 'Slaný' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -15131,7 +15131,7 @@
     <row r="22">
       <c r="C22" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Plzeň' → 'Moravské Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -15155,7 +15155,7 @@
     <row r="24">
       <c r="C24" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'SKP Rapid Plzeň' → 'Plzeň' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -15167,7 +15167,7 @@
     <row r="25">
       <c r="C25" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'RT Torax Poruba' → 'Poruba' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Ekonomické Stavby Plzeň' → 'Plzeň' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -15179,7 +15179,7 @@
     <row r="26">
       <c r="C26" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -15191,7 +15191,7 @@
     <row r="27">
       <c r="C27" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'UHK LEV Slaný' → 'Slaný' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'IHT Brimstones Cheb' → 'Cheb' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -15203,7 +15203,7 @@
     <row r="28">
       <c r="C28" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'PSK 96 Cheb' → 'Cheb' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -15215,7 +15215,7 @@
     <row r="29">
       <c r="C29" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -15227,7 +15227,7 @@
     <row r="30">
       <c r="C30" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'BK JTC Nová Paka' → 'Nová Paka' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -15239,7 +15239,7 @@
     <row r="31">
       <c r="C31" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Veselí nad Moravou' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Stadion Nový Bydžov' → 'Nový Bydžov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -15251,7 +15251,7 @@
     <row r="32">
       <c r="C32" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Závodní hokejové Pardubice' → 'Pardubice' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -15263,7 +15263,7 @@
     <row r="33">
       <c r="C33" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'SKP Rapid Plzeň' → 'Plzeň' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: K ověření, zda jde o B-tým nebo samostatný klub (Česká Třebová mohla mít dva různé kluby). Smart fix prev: 0650 (Sokol Česká Třebová = jiný klub) → 0656 (Perla II z 49/50 = B-tým Perly). Audit 04/2026.</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -15275,7 +15275,7 @@
     <row r="34">
       <c r="C34" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Ekonomické Stavby Plzeň' → 'Plzeň' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -15287,7 +15287,7 @@
     <row r="35">
       <c r="C35" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S2011_12_0063 (weak, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -15299,7 +15299,7 @@
     <row r="36">
       <c r="C36" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'IHT Brimstones Cheb' → 'Cheb' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'HCM Warrior Brno' → 'Brno' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -15311,7 +15311,7 @@
     <row r="37">
       <c r="C37" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'PSK 96 Cheb' → 'Cheb' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'RT Torax Poruba' → 'Poruba' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -15323,7 +15323,7 @@
     <row r="38">
       <c r="C38" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S2011_12_0067 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -15333,9 +15333,14 @@
       </c>
     </row>
     <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>NODE_S2012_13_0030</t>
+        </is>
+      </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'BK JTC Nová Paka' → 'Nová Paka' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] pyramida (feeds_into): top-level kvalifikace bez feeds_into: 'KVAL  skupina A'</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -15345,9 +15350,14 @@
       </c>
     </row>
     <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>NODE_S2012_13_0031</t>
+        </is>
+      </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Stadion Nový Bydžov' → 'Nový Bydžov' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] pyramida (feeds_into): top-level kvalifikace bez feeds_into: 'KVAL  skupina B'</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -15357,171 +15367,17 @@
       </c>
     </row>
     <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>NODE_S2012_13_0032</t>
+        </is>
+      </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Závodní hokejové Pardubice' → 'Pardubice' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] pyramida (feeds_into): top-level kvalifikace bez feeds_into: 'KVAL  skupina C'</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: K ověření, zda jde o B-tým nebo samostatný klub (Česká Třebová mohla mít dva různé kluby). Smart fix prev: 0650 (Sokol Česká Třebová = jiný klub) → 0656 (Perla II z 49/50 = B-tým Perly). Audit 04/2026.</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S2011_12_0063 (weak, jméno+město; verifikovat) [fix_continuity]</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'HCM Warrior Brno' → 'Brno' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'RT Torax Poruba' → 'Poruba' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S2011_12_0067 (strong, jméno+město; verifikovat) [fix_continuity]</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Havlíčkův Brod' → 'Rožnov pod Radhoštěm' (odvozeno z názvu klubu) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Havlíčkův Brod' → 'Rožnov pod Radhoštěm' (odvozeno z názvu klubu) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Havlíčkův Brod' → 'Rožnov pod Radhoštěm' (odvozeno z názvu klubu) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>NODE_S2012_13_0030</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>[TBD] pyramida (feeds_into): top-level kvalifikace bez feeds_into: 'KVAL  skupina A'</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>NODE_S2012_13_0031</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>[TBD] pyramida (feeds_into): top-level kvalifikace bez feeds_into: 'KVAL  skupina B'</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>NODE_S2012_13_0032</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>[TBD] pyramida (feeds_into): top-level kvalifikace bez feeds_into: 'KVAL  skupina C'</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
         <is>
           <t>TODO-auto</t>
         </is>
@@ -15596,7 +15452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K115"/>
+  <dimension ref="A1:L115"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15655,6 +15511,11 @@
           <t>note</t>
         </is>
       </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>prev_node_id</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -15697,6 +15558,11 @@
           <t>14 týmů (5 stat sloupců): základ + QF/SF/finále + baráž. Mistr: HC Škoda Plzeň.</t>
         </is>
       </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>NODE_S2011_12_0001</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -15744,6 +15610,11 @@
           <t>Vítězové 4 skupin II.ligy. Dvoukolově. Top 2 do I.ligy.</t>
         </is>
       </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>NODE_S2011_12_0002</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -15786,6 +15657,11 @@
           <t>I.ČNHL: základ + playoff (QF/SF/finále/O 3.) + O 5.-8. + o udržení. I.SNHL (12). Kval o I.ligu.</t>
         </is>
       </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>NODE_S2011_12_0003</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -15828,6 +15704,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>NODE_S2011_12_0004</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -15870,6 +15751,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>NODE_S2011_12_0005</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -15912,6 +15798,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>NODE_S2011_12_0006</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -15954,6 +15845,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>NODE_S2011_12_0007</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -15996,6 +15892,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>NODE_S2011_12_0008</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -16038,6 +15939,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>NODE_S2011_12_0009</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -16080,6 +15986,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>NODE_S2011_12_0010</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -16122,6 +16033,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>NODE_S2011_12_0011</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -16164,6 +16080,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>NODE_S2011_12_0012</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -16206,6 +16127,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>NODE_S2011_12_0013</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -16248,6 +16174,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>NODE_S2011_12_0014</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -16290,6 +16221,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>NODE_S2011_12_0015</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -16332,6 +16268,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>NODE_S2011_12_0016</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -16374,6 +16315,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>NODE_S2011_12_0017</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -16416,6 +16362,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>NODE_S2011_12_0018</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -16458,6 +16409,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>NODE_S2011_12_0019</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -16500,6 +16456,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>NODE_S2011_12_0020</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -16542,6 +16503,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>NODE_S2011_12_0021</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -16584,6 +16550,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>NODE_S2011_12_0022</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -16626,6 +16597,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>NODE_S2011_12_0023</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -16668,6 +16644,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>NODE_S2011_12_0024</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -16710,6 +16691,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>NODE_S2011_12_0025</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -16752,6 +16738,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>NODE_S2011_12_0026</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -16794,6 +16785,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>NODE_S2011_12_0027</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -16836,6 +16832,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>NODE_S2011_12_0028</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -16883,6 +16884,11 @@
           <t>Kvalifikace o postup do II.ligy</t>
         </is>
       </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>NODE_S2011_12_0029</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -16915,6 +16921,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>NODE_S2011_12_0030</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -16947,6 +16958,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>NODE_S2011_12_0031</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -16979,6 +16995,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>NODE_S2011_12_0032</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -17021,6 +17042,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>NODE_S2011_12_0033</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -17273,6 +17299,11 @@
           <t>II.liga: 2 skupiny + finále + o postup do I.ligy.</t>
         </is>
       </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>NODE_S2011_12_0036</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -17315,6 +17346,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>NODE_S2011_12_0037</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -17357,6 +17393,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>NODE_S2011_12_0038</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -17399,6 +17440,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>NODE_S2011_12_0039</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -17441,6 +17487,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>NODE_S2011_12_0040</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -17483,6 +17534,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>NODE_S2011_12_0041</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -17525,6 +17581,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>NODE_S2011_12_0042</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -17567,6 +17628,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>NODE_S2011_12_0043</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -17609,6 +17675,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>NODE_S2011_12_0044</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -17651,6 +17722,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>NODE_S2011_12_0045</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -17693,6 +17769,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>NODE_S2011_12_0046</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -17735,6 +17816,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>NODE_S2011_12_0047</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -17777,6 +17863,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>NODE_S2011_12_0048</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -17819,6 +17910,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>NODE_S2011_12_0049</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -17861,6 +17957,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>NODE_S2011_12_0050</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -17903,6 +18004,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>NODE_S2011_12_0049</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -17987,6 +18093,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>NODE_S2011_12_0051</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -18029,6 +18140,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>NODE_S2011_12_0052</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -18071,6 +18187,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>NODE_S2011_12_0053</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -18113,6 +18234,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>NODE_S2011_12_0054</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -18239,6 +18365,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>NODE_S2011_12_0055</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -18323,6 +18454,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>NODE_S2011_12_0057</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -18407,6 +18543,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>NODE_S2011_12_0059</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -18491,6 +18632,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>NODE_S2011_12_0061</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -18575,6 +18721,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>NODE_S2011_12_0063</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -18659,6 +18810,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>NODE_S2011_12_0066</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -18701,6 +18857,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>NODE_S2011_12_0066</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -18785,6 +18946,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>NODE_S2011_12_0067</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -18911,6 +19077,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>NODE_S2011_12_0068</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -18953,6 +19124,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>NODE_S2011_12_0069</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -19079,6 +19255,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>NODE_S2011_12_0072</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -19499,6 +19680,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>NODE_S2011_12_0078</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -19541,6 +19727,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>NODE_S2011_12_0079</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -19625,6 +19816,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>NODE_S2011_12_0080</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -19751,6 +19947,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>NODE_S2011_12_0083</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -19793,6 +19994,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>NODE_S2011_12_0084</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -19833,6 +20039,11 @@
       <c r="J101" t="inlineStr">
         <is>
           <t>complete</t>
+        </is>
+      </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>NODE_S2011_12_0085</t>
         </is>
       </c>
     </row>
@@ -19856,6 +20067,11 @@
           <t>I.liga (10 týmů, jeden stůl)</t>
         </is>
       </c>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>L10</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -19873,6 +20089,11 @@
           <t>NODE_S2012_13_0001</t>
         </is>
       </c>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>L20</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -19890,6 +20111,11 @@
           <t>NODE_S2012_13_0003</t>
         </is>
       </c>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t>L25</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -19907,6 +20133,11 @@
           <t>NODE_S2012_13_0003</t>
         </is>
       </c>
+      <c r="L108" t="inlineStr">
+        <is>
+          <t>L30</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -19924,6 +20155,11 @@
           <t>NODE_S2012_13_0039</t>
         </is>
       </c>
+      <c r="L109" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -19934,6 +20170,11 @@
       <c r="B110" t="inlineStr">
         <is>
           <t>Okresní přebory (jen registr)</t>
+        </is>
+      </c>
+      <c r="L110" t="inlineStr">
+        <is>
+          <t>okresní</t>
         </is>
       </c>
     </row>
@@ -26066,12 +26307,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň. || TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň.</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Plzeň</t>
         </is>
       </c>
     </row>
@@ -26370,12 +26611,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov. || TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov.</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Mladá Boleslav</t>
+          <t>Chomutov</t>
         </is>
       </c>
     </row>
@@ -26622,12 +26863,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov. || TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov.</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Hradec Králové</t>
+          <t>Prostějov</t>
         </is>
       </c>
     </row>
@@ -27264,12 +27505,12 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Veselí nad Moravou = TJ Lokomotiva Veselí nad Moravou (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Hodonín). Železničárský klub. NE Veselí nad Lužnicí (Jihocesky). city Veselí nad Moravou. || TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach] || TBD: city 'Veselí nad Moravou' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Veselí nad Moravou = TJ Lokomotiva Veselí nad Moravou (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Hodonín). Železničárský klub. NE Veselí nad Lužnicí (Jihocesky). city Veselí nad Moravou. || TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Veselí nad Lužnicí</t>
+          <t>Veselí nad Moravou</t>
         </is>
       </c>
     </row>
@@ -28366,12 +28607,12 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov. || TBD: city 'Chomutov' → 'SC Kolín' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov.</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>SC Kolín</t>
+          <t>Chomutov</t>
         </is>
       </c>
     </row>
@@ -28534,12 +28775,12 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň. || TBD: city 'Plzeň' → 'Moravské Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň.</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>Moravské Budějovice</t>
+          <t>Plzeň</t>
         </is>
       </c>
     </row>
@@ -29075,12 +29316,12 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov. || TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov.</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>Mladá Boleslav</t>
+          <t>Chomutov</t>
         </is>
       </c>
     </row>
@@ -29888,12 +30129,12 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň. || TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň.</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Plzeň</t>
         </is>
       </c>
     </row>
@@ -29977,12 +30218,12 @@
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>Veselí nad Moravou = TJ Lokomotiva Veselí nad Moravou (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Hodonín). Železničárský klub. NE Veselí nad Lužnicí (Jihocesky). city Veselí nad Moravou. || TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach] || TBD: city 'Veselí nad Moravou' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Veselí nad Moravou = TJ Lokomotiva Veselí nad Moravou (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Hodonín). Železničárský klub. NE Veselí nad Lužnicí (Jihocesky). city Veselí nad Moravou. || TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>Veselí nad Lužnicí</t>
+          <t>Veselí nad Moravou</t>
         </is>
       </c>
     </row>
@@ -35920,12 +36161,12 @@
       </c>
       <c r="I241" t="inlineStr">
         <is>
-          <t>Jiskra Havlíčkův Brod = HC Rebel HB (Wiki D42 - registr ustavy 04/2026). city Havlíčkův Brod. || TBD: city 'Havlíčkův Brod' → 'Rožnov pod Radhoštěm' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Jiskra Havlíčkův Brod = HC Rebel HB (Wiki D42 - registr ustavy 04/2026). city Havlíčkův Brod.</t>
         </is>
       </c>
       <c r="J241" t="inlineStr">
         <is>
-          <t>Rožnov pod Radhoštěm</t>
+          <t>Havlíčkův Brod</t>
         </is>
       </c>
     </row>
@@ -36009,12 +36250,12 @@
       </c>
       <c r="I243" t="inlineStr">
         <is>
-          <t>Jiskra Havlíčkův Brod = HC Rebel HB (Wiki D42 - registr ustavy 04/2026). city Havlíčkův Brod. || TBD: city 'Havlíčkův Brod' → 'Rožnov pod Radhoštěm' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Jiskra Havlíčkův Brod = HC Rebel HB (Wiki D42 - registr ustavy 04/2026). city Havlíčkův Brod.</t>
         </is>
       </c>
       <c r="J243" t="inlineStr">
         <is>
-          <t>Rožnov pod Radhoštěm</t>
+          <t>Havlíčkův Brod</t>
         </is>
       </c>
     </row>
@@ -36093,12 +36334,12 @@
       </c>
       <c r="I245" t="inlineStr">
         <is>
-          <t>Jiskra Havlíčkův Brod = HC Rebel HB (Wiki D42 - registr ustavy 04/2026). city Havlíčkův Brod. || TBD: city 'Havlíčkův Brod' → 'Rožnov pod Radhoštěm' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Jiskra Havlíčkův Brod = HC Rebel HB (Wiki D42 - registr ustavy 04/2026). city Havlíčkův Brod.</t>
         </is>
       </c>
       <c r="J245" t="inlineStr">
         <is>
-          <t>Rožnov pod Radhoštěm</t>
+          <t>Havlíčkův Brod</t>
         </is>
       </c>
     </row>
@@ -36343,7 +36584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F49"/>
+  <dimension ref="A1:F37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -36417,12 +36658,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>CLUB_S2012_13_0008</t>
+          <t>CLUB_S2012_13_0014</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'KLH VT VTJ Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -36437,12 +36678,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>CLUB_S2012_13_0014</t>
+          <t>CLUB_S2012_13_0021</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>TBD: city 'KLH VT VTJ Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Sportovní klub Kadaň' → 'Kadaň' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -36457,12 +36698,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>CLUB_S2012_13_0015</t>
+          <t>CLUB_S2012_13_0032</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'VSK Technika Brno' → 'Technika Brno' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -36477,12 +36718,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>CLUB_S2012_13_0021</t>
+          <t>CLUB_S2012_13_0035</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>TBD: city 'Sportovní klub Kadaň' → 'Kadaň' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
         </is>
       </c>
     </row>
@@ -36497,12 +36738,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>CLUB_S2012_13_0023</t>
+          <t>CLUB_S2012_13_0039</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -36517,12 +36758,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>CLUB_S2012_13_0032</t>
+          <t>CLUB_S2012_13_0057</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>TBD: city 'VSK Technika Brno' → 'Technika Brno' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'SHC Maso Brejcha Klatovy' → 'Klatovy' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -36537,12 +36778,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>CLUB_S2012_13_0035</t>
+          <t>CLUB_S2012_13_0058</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
+          <t>TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -36557,12 +36798,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>CLUB_S2012_13_0039</t>
+          <t>CLUB_S2012_13_0061</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Vlci Jablonec nad Nisou' → 'Jablonec nad Nisou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -36577,12 +36818,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>CLUB_S2012_13_0039</t>
+          <t>CLUB_S2012_13_0068</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>TBD: city 'Veselí nad Moravou' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'NED Hockey Nymburk' → 'Nymburk' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -36597,12 +36838,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>CLUB_S2012_13_0057</t>
+          <t>CLUB_S2012_13_0070</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>TBD: city 'SHC Maso Brejcha Klatovy' → 'Klatovy' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -36617,12 +36858,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>CLUB_S2012_13_0058</t>
+          <t>CLUB_S2012_13_0072</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -36637,12 +36878,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>CLUB_S2012_13_0061</t>
+          <t>CLUB_S2012_13_0073</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>TBD: city 'Vlci Jablonec nad Nisou' → 'Jablonec nad Nisou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -36657,12 +36898,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>CLUB_S2012_13_0067</t>
+          <t>CLUB_S2012_13_0077</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>TBD: city 'Chomutov' → 'SC Kolín' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'RT Torax Poruba' → 'Poruba' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -36677,12 +36918,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>CLUB_S2012_13_0068</t>
+          <t>CLUB_S2012_13_0089</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>TBD: city 'NED Hockey Nymburk' → 'Nymburk' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'UHK LEV Slaný' → 'Slaný' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -36697,7 +36938,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>CLUB_S2012_13_0070</t>
+          <t>CLUB_S2012_13_0092</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
@@ -36717,12 +36958,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>CLUB_S2012_13_0071</t>
+          <t>CLUB_S2012_13_0107</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>TBD: city 'Plzeň' → 'Moravské Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -36737,7 +36978,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>CLUB_S2012_13_0072</t>
+          <t>CLUB_S2012_13_0116</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
@@ -36757,12 +36998,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>CLUB_S2012_13_0073</t>
+          <t>CLUB_S2012_13_0148</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
+          <t>TBD: city 'SKP Rapid Plzeň' → 'Plzeň' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -36777,12 +37018,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>CLUB_S2012_13_0077</t>
+          <t>CLUB_S2012_13_0156</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>TBD: city 'RT Torax Poruba' → 'Poruba' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Ekonomické Stavby Plzeň' → 'Plzeň' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -36797,12 +37038,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>CLUB_S2012_13_0085</t>
+          <t>CLUB_S2012_13_0175</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
         </is>
       </c>
     </row>
@@ -36817,12 +37058,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>CLUB_S2012_13_0089</t>
+          <t>CLUB_S2012_13_0189</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>TBD: city 'UHK LEV Slaný' → 'Slaný' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'IHT Brimstones Cheb' → 'Cheb' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -36837,12 +37078,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>CLUB_S2012_13_0092</t>
+          <t>CLUB_S2012_13_0191</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
+          <t>TBD: city 'PSK 96 Cheb' → 'Cheb' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -36857,12 +37098,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>CLUB_S2012_13_0105</t>
+          <t>CLUB_S2012_13_0205</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
         </is>
       </c>
     </row>
@@ -36877,12 +37118,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>CLUB_S2012_13_0107</t>
+          <t>CLUB_S2012_13_0206</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'BK JTC Nová Paka' → 'Nová Paka' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -36897,12 +37138,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>CLUB_S2012_13_0107</t>
+          <t>CLUB_S2012_13_0208</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>TBD: city 'Veselí nad Moravou' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'Stadion Nový Bydžov' → 'Nový Bydžov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -36917,12 +37158,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>CLUB_S2012_13_0116</t>
+          <t>CLUB_S2012_13_0221</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Závodní hokejové Pardubice' → 'Pardubice' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -36937,12 +37178,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>CLUB_S2012_13_0148</t>
+          <t>CLUB_S2012_13_0222</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>TBD: city 'SKP Rapid Plzeň' → 'Plzeň' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: K ověření, zda jde o B-tým nebo samostatný klub (Česká Třebová mohla mít dva různé kluby). Smart fix prev: 0650 (Sokol Česká Třebová = jiný klub) → 0656 (Perla II z 49/50 = B-tým Perly). Audit 04/2026.</t>
         </is>
       </c>
     </row>
@@ -36957,12 +37198,12 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>CLUB_S2012_13_0156</t>
+          <t>CLUB_S2012_13_0223</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>TBD: city 'Ekonomické Stavby Plzeň' → 'Plzeň' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
         </is>
       </c>
     </row>
@@ -36977,12 +37218,12 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>CLUB_S2012_13_0175</t>
+          <t>CLUB_S2012_13_0235</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S2011_12_0063 (weak, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
     </row>
@@ -36997,12 +37238,12 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>CLUB_S2012_13_0189</t>
+          <t>CLUB_S2012_13_0243</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>TBD: city 'IHT Brimstones Cheb' → 'Cheb' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'HCM Warrior Brno' → 'Brno' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -37017,12 +37258,12 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>CLUB_S2012_13_0191</t>
+          <t>CLUB_S2012_13_0259</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>TBD: city 'PSK 96 Cheb' → 'Cheb' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'RT Torax Poruba' → 'Poruba' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -37037,12 +37278,12 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>CLUB_S2012_13_0205</t>
+          <t>CLUB_S2012_13_0261</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S2011_12_0067 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
     </row>
@@ -37052,17 +37293,17 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>prev_club_id / identita</t>
+          <t>pyramida (feeds_into)</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>CLUB_S2012_13_0206</t>
+          <t>NODE_S2012_13_0030</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>TBD: city 'BK JTC Nová Paka' → 'Nová Paka' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>top-level kvalifikace bez feeds_into: 'KVAL  skupina A'</t>
         </is>
       </c>
     </row>
@@ -37072,17 +37313,17 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>prev_club_id / identita</t>
+          <t>pyramida (feeds_into)</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>CLUB_S2012_13_0208</t>
+          <t>NODE_S2012_13_0031</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>TBD: city 'Stadion Nový Bydžov' → 'Nový Bydžov' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>top-level kvalifikace bez feeds_into: 'KVAL  skupina B'</t>
         </is>
       </c>
     </row>
@@ -37092,262 +37333,22 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>prev_club_id / identita</t>
+          <t>pyramida (feeds_into)</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>CLUB_S2012_13_0221</t>
+          <t>NODE_S2012_13_0032</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>TBD: city 'Závodní hokejové Pardubice' → 'Pardubice' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="n">
-        <v>37</v>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>CLUB_S2012_13_0222</t>
-        </is>
-      </c>
-      <c r="D38" s="5" t="inlineStr">
-        <is>
-          <t>TBD: K ověření, zda jde o B-tým nebo samostatný klub (Česká Třebová mohla mít dva různé kluby). Smart fix prev: 0650 (Sokol Česká Třebová = jiný klub) → 0656 (Perla II z 49/50 = B-tým Perly). Audit 04/2026.</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="n">
-        <v>38</v>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>CLUB_S2012_13_0223</t>
-        </is>
-      </c>
-      <c r="D39" s="5" t="inlineStr">
-        <is>
-          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="n">
-        <v>39</v>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>CLUB_S2012_13_0235</t>
-        </is>
-      </c>
-      <c r="D40" s="5" t="inlineStr">
-        <is>
-          <t>TBD: auto-prev_club_id doplnění → CLUB_S2011_12_0063 (weak, jméno+město; verifikovat) [fix_continuity]</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="n">
-        <v>40</v>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>CLUB_S2012_13_0243</t>
-        </is>
-      </c>
-      <c r="D41" s="5" t="inlineStr">
-        <is>
-          <t>TBD: city 'HCM Warrior Brno' → 'Brno' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="n">
-        <v>41</v>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>CLUB_S2012_13_0259</t>
-        </is>
-      </c>
-      <c r="D42" s="5" t="inlineStr">
-        <is>
-          <t>TBD: city 'RT Torax Poruba' → 'Poruba' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="n">
-        <v>42</v>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>CLUB_S2012_13_0261</t>
-        </is>
-      </c>
-      <c r="D43" s="5" t="inlineStr">
-        <is>
-          <t>TBD: auto-prev_club_id doplnění → CLUB_S2011_12_0067 (strong, jméno+město; verifikovat) [fix_continuity]</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="n">
-        <v>43</v>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>CLUB_S2012_13_0262</t>
-        </is>
-      </c>
-      <c r="D44" s="5" t="inlineStr">
-        <is>
-          <t>TBD: city 'Havlíčkův Brod' → 'Rožnov pod Radhoštěm' (odvozeno z názvu klubu) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="n">
-        <v>44</v>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>CLUB_S2012_13_0264</t>
-        </is>
-      </c>
-      <c r="D45" s="5" t="inlineStr">
-        <is>
-          <t>TBD: city 'Havlíčkův Brod' → 'Rožnov pod Radhoštěm' (odvozeno z názvu klubu) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="n">
-        <v>45</v>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>CLUB_S2012_13_0266</t>
-        </is>
-      </c>
-      <c r="D46" s="5" t="inlineStr">
-        <is>
-          <t>TBD: city 'Havlíčkův Brod' → 'Rožnov pod Radhoštěm' (odvozeno z názvu klubu) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="n">
-        <v>46</v>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>pyramida (feeds_into)</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>NODE_S2012_13_0030</t>
-        </is>
-      </c>
-      <c r="D47" s="5" t="inlineStr">
-        <is>
-          <t>top-level kvalifikace bez feeds_into: 'KVAL  skupina A'</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="n">
-        <v>47</v>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>pyramida (feeds_into)</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>NODE_S2012_13_0031</t>
-        </is>
-      </c>
-      <c r="D48" s="5" t="inlineStr">
-        <is>
-          <t>top-level kvalifikace bez feeds_into: 'KVAL  skupina B'</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="n">
-        <v>48</v>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>pyramida (feeds_into)</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>NODE_S2012_13_0032</t>
-        </is>
-      </c>
-      <c r="D49" s="5" t="inlineStr">
-        <is>
           <t>top-level kvalifikace bez feeds_into: 'KVAL  skupina C'</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F49"/>
+  <autoFilter ref="A1:F37"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/data/S2012_13_FINAL.xlsx
+++ b/data/S2012_13_FINAL.xlsx
@@ -32,7 +32,7 @@
     <sheet name="TODO" sheetId="23" state="visible" r:id="rId23"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="22" hidden="1">'TODO'!$A$1:$F$37</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="22" hidden="1">'TODO'!$A$1:$F$38</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -14798,7 +14798,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E41"/>
+  <dimension ref="A1:E44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14937,33 +14937,43 @@
       </c>
     </row>
     <row r="6">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>30PLZN</t>
+        </is>
+      </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[club-fate] 1.LHC Kralovice 1991 — odstoupily</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>TODO-auto</t>
+          <t>club-note-extracted</t>
         </is>
       </c>
     </row>
     <row r="7">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>30PLZN</t>
+        </is>
+      </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'KLH VT VTJ Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[club-fate] HC Dolní Kamenice — odstoupila (club_id: CLUB_S2012_13_0170)</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>TODO-auto</t>
+          <t>club-note-extracted</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="C8" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Sportovní klub Kadaň' → 'Kadaň' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -14975,7 +14985,7 @@
     <row r="9">
       <c r="C9" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'VSK Technika Brno' → 'Technika Brno' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'KLH VT VTJ Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -14987,7 +14997,7 @@
     <row r="10">
       <c r="C10" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Sportovní klub Kadaň' → 'Kadaň' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -14999,7 +15009,7 @@
     <row r="11">
       <c r="C11" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'VSK Technika Brno' → 'Technika Brno' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -15011,7 +15021,7 @@
     <row r="12">
       <c r="C12" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'SHC Maso Brejcha Klatovy' → 'Klatovy' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -15023,7 +15033,7 @@
     <row r="13">
       <c r="C13" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -15035,7 +15045,7 @@
     <row r="14">
       <c r="C14" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Vlci Jablonec nad Nisou' → 'Jablonec nad Nisou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'SHC Maso Brejcha Klatovy' → 'Klatovy' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -15047,7 +15057,7 @@
     <row r="15">
       <c r="C15" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'NED Hockey Nymburk' → 'Nymburk' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -15059,7 +15069,7 @@
     <row r="16">
       <c r="C16" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vlci Jablonec nad Nisou' → 'Jablonec nad Nisou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -15071,7 +15081,7 @@
     <row r="17">
       <c r="C17" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'NED Hockey Nymburk' → 'Nymburk' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -15095,7 +15105,7 @@
     <row r="19">
       <c r="C19" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'RT Torax Poruba' → 'Poruba' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -15107,7 +15117,7 @@
     <row r="20">
       <c r="C20" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'UHK LEV Slaný' → 'Slaný' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -15119,7 +15129,7 @@
     <row r="21">
       <c r="C21" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'RT Torax Poruba' → 'Poruba' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -15131,7 +15141,7 @@
     <row r="22">
       <c r="C22" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'UHK LEV Slaný' → 'Slaný' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -15143,7 +15153,7 @@
     <row r="23">
       <c r="C23" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -15155,7 +15165,7 @@
     <row r="24">
       <c r="C24" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'SKP Rapid Plzeň' → 'Plzeň' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -15167,7 +15177,7 @@
     <row r="25">
       <c r="C25" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Ekonomické Stavby Plzeň' → 'Plzeň' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -15179,7 +15189,7 @@
     <row r="26">
       <c r="C26" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'SKP Rapid Plzeň' → 'Plzeň' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -15191,7 +15201,7 @@
     <row r="27">
       <c r="C27" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'IHT Brimstones Cheb' → 'Cheb' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Ekonomické Stavby Plzeň' → 'Plzeň' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -15203,7 +15213,7 @@
     <row r="28">
       <c r="C28" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'PSK 96 Cheb' → 'Cheb' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: extrahováno z block_name: 'HC Dolní Kamenice — odstoupila' [fix_club_notes_in_block_name]</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -15215,7 +15225,7 @@
     <row r="29">
       <c r="C29" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
+          <t>[TBD] prev_club_id / identita: TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -15227,7 +15237,7 @@
     <row r="30">
       <c r="C30" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'BK JTC Nová Paka' → 'Nová Paka' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'IHT Brimstones Cheb' → 'Cheb' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -15239,7 +15249,7 @@
     <row r="31">
       <c r="C31" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Stadion Nový Bydžov' → 'Nový Bydžov' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'PSK 96 Cheb' → 'Cheb' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -15251,7 +15261,7 @@
     <row r="32">
       <c r="C32" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Závodní hokejové Pardubice' → 'Pardubice' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -15263,7 +15273,7 @@
     <row r="33">
       <c r="C33" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: K ověření, zda jde o B-tým nebo samostatný klub (Česká Třebová mohla mít dva různé kluby). Smart fix prev: 0650 (Sokol Česká Třebová = jiný klub) → 0656 (Perla II z 49/50 = B-tým Perly). Audit 04/2026.</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'BK JTC Nová Paka' → 'Nová Paka' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -15275,7 +15285,7 @@
     <row r="34">
       <c r="C34" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Stadion Nový Bydžov' → 'Nový Bydžov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -15287,7 +15297,7 @@
     <row r="35">
       <c r="C35" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S2011_12_0063 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Závodní hokejové Pardubice' → 'Pardubice' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -15299,7 +15309,7 @@
     <row r="36">
       <c r="C36" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'HCM Warrior Brno' → 'Brno' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: K ověření, zda jde o B-tým nebo samostatný klub (Česká Třebová mohla mít dva různé kluby). Smart fix prev: 0650 (Sokol Česká Třebová = jiný klub) → 0656 (Perla II z 49/50 = B-tým Perly). Audit 04/2026.</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -15311,7 +15321,7 @@
     <row r="37">
       <c r="C37" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'RT Torax Poruba' → 'Poruba' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -15323,61 +15333,97 @@
     <row r="38">
       <c r="C38" t="inlineStr">
         <is>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S2011_12_0063 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'HCM Warrior Brno' → 'Brno' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'RT Torax Poruba' → 'Poruba' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="C41" t="inlineStr">
+        <is>
           <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S2011_12_0067 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr">
+      <c r="D41" t="inlineStr">
         <is>
           <t>TODO-auto</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
+    <row r="42">
+      <c r="A42" t="inlineStr">
         <is>
           <t>NODE_S2012_13_0030</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
+      <c r="C42" t="inlineStr">
         <is>
           <t>[TBD] pyramida (feeds_into): top-level kvalifikace bez feeds_into: 'KVAL  skupina A'</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr">
+      <c r="D42" t="inlineStr">
         <is>
           <t>TODO-auto</t>
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
+    <row r="43">
+      <c r="A43" t="inlineStr">
         <is>
           <t>NODE_S2012_13_0031</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
+      <c r="C43" t="inlineStr">
         <is>
           <t>[TBD] pyramida (feeds_into): top-level kvalifikace bez feeds_into: 'KVAL  skupina B'</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr">
+      <c r="D43" t="inlineStr">
         <is>
           <t>TODO-auto</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
+    <row r="44">
+      <c r="A44" t="inlineStr">
         <is>
           <t>NODE_S2012_13_0032</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
+      <c r="C44" t="inlineStr">
         <is>
           <t>[TBD] pyramida (feeds_into): top-level kvalifikace bez feeds_into: 'KVAL  skupina C'</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr">
+      <c r="D44" t="inlineStr">
         <is>
           <t>TODO-auto</t>
         </is>
@@ -32820,7 +32866,7 @@
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>Dolní Kamenice = HC Dolní Kamenice (Wiki D42 - registr ustavy 04/2026). Plzensky kraj (okres Domazlice). POZOR: vícero. city Dolní Kamenice.</t>
+          <t>Dolní Kamenice = HC Dolní Kamenice (Wiki D42 - registr ustavy 04/2026). Plzensky kraj (okres Domazlice). POZOR: vícero. city Dolní Kamenice. || TBD: extrahováno z block_name: 'HC Dolní Kamenice — odstoupila' [fix_club_notes_in_block_name]</t>
         </is>
       </c>
       <c r="J163" t="inlineStr">
@@ -36584,7 +36630,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F37"/>
+  <dimension ref="A1:F38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -37038,12 +37084,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>CLUB_S2012_13_0175</t>
+          <t>CLUB_S2012_13_0170</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
+          <t>TBD: extrahováno z block_name: 'HC Dolní Kamenice — odstoupila' [fix_club_notes_in_block_name]</t>
         </is>
       </c>
     </row>
@@ -37058,12 +37104,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>CLUB_S2012_13_0189</t>
+          <t>CLUB_S2012_13_0175</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>TBD: city 'IHT Brimstones Cheb' → 'Cheb' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
         </is>
       </c>
     </row>
@@ -37078,12 +37124,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>CLUB_S2012_13_0191</t>
+          <t>CLUB_S2012_13_0189</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>TBD: city 'PSK 96 Cheb' → 'Cheb' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'IHT Brimstones Cheb' → 'Cheb' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -37098,12 +37144,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>CLUB_S2012_13_0205</t>
+          <t>CLUB_S2012_13_0191</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
+          <t>TBD: city 'PSK 96 Cheb' → 'Cheb' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -37118,12 +37164,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>CLUB_S2012_13_0206</t>
+          <t>CLUB_S2012_13_0205</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>TBD: city 'BK JTC Nová Paka' → 'Nová Paka' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
         </is>
       </c>
     </row>
@@ -37138,12 +37184,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>CLUB_S2012_13_0208</t>
+          <t>CLUB_S2012_13_0206</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>TBD: city 'Stadion Nový Bydžov' → 'Nový Bydžov' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'BK JTC Nová Paka' → 'Nová Paka' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -37158,12 +37204,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>CLUB_S2012_13_0221</t>
+          <t>CLUB_S2012_13_0208</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>TBD: city 'Závodní hokejové Pardubice' → 'Pardubice' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Stadion Nový Bydžov' → 'Nový Bydžov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -37178,12 +37224,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>CLUB_S2012_13_0222</t>
+          <t>CLUB_S2012_13_0221</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>TBD: K ověření, zda jde o B-tým nebo samostatný klub (Česká Třebová mohla mít dva různé kluby). Smart fix prev: 0650 (Sokol Česká Třebová = jiný klub) → 0656 (Perla II z 49/50 = B-tým Perly). Audit 04/2026.</t>
+          <t>TBD: city 'Závodní hokejové Pardubice' → 'Pardubice' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -37198,12 +37244,12 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>CLUB_S2012_13_0223</t>
+          <t>CLUB_S2012_13_0222</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
+          <t>TBD: K ověření, zda jde o B-tým nebo samostatný klub (Česká Třebová mohla mít dva různé kluby). Smart fix prev: 0650 (Sokol Česká Třebová = jiný klub) → 0656 (Perla II z 49/50 = B-tým Perly). Audit 04/2026.</t>
         </is>
       </c>
     </row>
@@ -37218,12 +37264,12 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>CLUB_S2012_13_0235</t>
+          <t>CLUB_S2012_13_0223</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>TBD: auto-prev_club_id doplnění → CLUB_S2011_12_0063 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
         </is>
       </c>
     </row>
@@ -37238,12 +37284,12 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>CLUB_S2012_13_0243</t>
+          <t>CLUB_S2012_13_0235</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>TBD: city 'HCM Warrior Brno' → 'Brno' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S2011_12_0063 (weak, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
     </row>
@@ -37258,12 +37304,12 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>CLUB_S2012_13_0259</t>
+          <t>CLUB_S2012_13_0243</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>TBD: city 'RT Torax Poruba' → 'Poruba' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'HCM Warrior Brno' → 'Brno' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -37278,12 +37324,12 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>CLUB_S2012_13_0261</t>
+          <t>CLUB_S2012_13_0259</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>TBD: auto-prev_club_id doplnění → CLUB_S2011_12_0067 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>TBD: city 'RT Torax Poruba' → 'Poruba' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -37293,17 +37339,17 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>pyramida (feeds_into)</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>NODE_S2012_13_0030</t>
+          <t>CLUB_S2012_13_0261</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>top-level kvalifikace bez feeds_into: 'KVAL  skupina A'</t>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S2011_12_0067 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
     </row>
@@ -37318,12 +37364,12 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>NODE_S2012_13_0031</t>
+          <t>NODE_S2012_13_0030</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>top-level kvalifikace bez feeds_into: 'KVAL  skupina B'</t>
+          <t>top-level kvalifikace bez feeds_into: 'KVAL  skupina A'</t>
         </is>
       </c>
     </row>
@@ -37338,17 +37384,37 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
+          <t>NODE_S2012_13_0031</t>
+        </is>
+      </c>
+      <c r="D37" s="5" t="inlineStr">
+        <is>
+          <t>top-level kvalifikace bez feeds_into: 'KVAL  skupina B'</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>pyramida (feeds_into)</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
           <t>NODE_S2012_13_0032</t>
         </is>
       </c>
-      <c r="D37" s="5" t="inlineStr">
+      <c r="D38" s="5" t="inlineStr">
         <is>
           <t>top-level kvalifikace bez feeds_into: 'KVAL  skupina C'</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F37"/>
+  <autoFilter ref="A1:F38"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -50697,7 +50763,7 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>skupina A / 1.LHC Kralovice 1991 — odstoupily</t>
+          <t>skupina A</t>
         </is>
       </c>
       <c r="C35" s="2" t="n"/>
@@ -55516,7 +55582,7 @@
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>skupina D / HC Dolní Kamenice — odstoupila</t>
+          <t>skupina D</t>
         </is>
       </c>
       <c r="C115" s="2" t="n"/>

--- a/data/S2012_13_FINAL.xlsx
+++ b/data/S2012_13_FINAL.xlsx
@@ -15498,7 +15498,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L115"/>
+  <dimension ref="A1:N115"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15562,6 +15562,16 @@
           <t>prev_node_id</t>
         </is>
       </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>entry</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>phase_order</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -20093,8 +20103,6 @@
         </is>
       </c>
     </row>
-    <row r="102"/>
-    <row r="103"/>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
@@ -20224,7 +20232,6 @@
         </is>
       </c>
     </row>
-    <row r="111"/>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>

--- a/data/S2012_13_FINAL.xlsx
+++ b/data/S2012_13_FINAL.xlsx
@@ -15750,6 +15750,16 @@
           <t>NODE_S2012_13_0001</t>
         </is>
       </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>NODE_S2012_13_0010</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>NODE_S2012_13_0016</t>
+        </is>
+      </c>
       <c r="I5" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -15764,6 +15774,14 @@
         <is>
           <t>NODE_S2011_12_0004</t>
         </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>14 týmů</t>
+        </is>
+      </c>
+      <c r="N5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -15938,6 +15956,16 @@
           <t>NODE_S2012_13_0007</t>
         </is>
       </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>NODE_S2012_13_0010</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>NODE_S2012_13_0019</t>
+        </is>
+      </c>
       <c r="I9" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -15952,6 +15980,14 @@
         <is>
           <t>NODE_S2011_12_0008</t>
         </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>horní část ZČ</t>
+        </is>
+      </c>
+      <c r="N9" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -16032,6 +16068,16 @@
           <t>NODE_S2012_13_0007</t>
         </is>
       </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>NODE_S2012_13_0011</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>NODE_S2012_13_0019</t>
+        </is>
+      </c>
       <c r="I11" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -16046,6 +16092,14 @@
         <is>
           <t>NODE_S2011_12_0010</t>
         </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>horní polovina ZČ</t>
+        </is>
+      </c>
+      <c r="N11" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="12">
@@ -16079,6 +16133,16 @@
           <t>NODE_S2012_13_0007</t>
         </is>
       </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>NODE_S2012_13_0015</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>NODE_S2012_13_0014</t>
+        </is>
+      </c>
       <c r="I12" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -16093,6 +16157,14 @@
         <is>
           <t>NODE_S2011_12_0011</t>
         </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>vítězové ČF</t>
+        </is>
+      </c>
+      <c r="N12" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="13">
@@ -16126,6 +16198,8 @@
           <t>NODE_S2012_13_0007</t>
         </is>
       </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -16140,6 +16214,14 @@
         <is>
           <t>NODE_S2011_12_0012</t>
         </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>sk. o 5.–8. (dolní)</t>
+        </is>
+      </c>
+      <c r="N13" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="14">
@@ -16173,6 +16255,8 @@
           <t>NODE_S2012_13_0007</t>
         </is>
       </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -16187,6 +16271,14 @@
         <is>
           <t>NODE_S2011_12_0013</t>
         </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>sk. o 5.–8. (horní)</t>
+        </is>
+      </c>
+      <c r="N14" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="15">
@@ -16220,6 +16312,8 @@
           <t>NODE_S2012_13_0007</t>
         </is>
       </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -16234,6 +16328,14 @@
         <is>
           <t>NODE_S2011_12_0014</t>
         </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>poražení SF</t>
+        </is>
+      </c>
+      <c r="N15" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="16">
@@ -16267,6 +16369,8 @@
           <t>NODE_S2012_13_0007</t>
         </is>
       </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -16281,6 +16385,14 @@
         <is>
           <t>NODE_S2011_12_0015</t>
         </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N16" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="17">
@@ -16314,6 +16426,8 @@
           <t>NODE_S2012_13_0001</t>
         </is>
       </c>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -16328,6 +16442,14 @@
         <is>
           <t>NODE_S2011_12_0016</t>
         </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>dolní část ZČ</t>
+        </is>
+      </c>
+      <c r="N17" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="18">
@@ -16361,6 +16483,8 @@
           <t>NODE_S2012_13_0007</t>
         </is>
       </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -16375,6 +16499,14 @@
         <is>
           <t>NODE_S2011_12_0017</t>
         </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>poražení play-off</t>
+        </is>
+      </c>
+      <c r="N18" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="19">
@@ -16408,6 +16540,8 @@
           <t>NODE_S2012_13_0007</t>
         </is>
       </c>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -16422,6 +16556,14 @@
         <is>
           <t>NODE_S2011_12_0018</t>
         </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>o 9. místo</t>
+        </is>
+      </c>
+      <c r="N19" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="20">
@@ -16455,6 +16597,16 @@
           <t>NODE_S2012_13_0007</t>
         </is>
       </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>NODE_S2012_13_0013</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>NODE_S2012_13_0012</t>
+        </is>
+      </c>
       <c r="I20" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -16469,6 +16621,14 @@
         <is>
           <t>NODE_S2011_12_0019</t>
         </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>poražení ČF</t>
+        </is>
+      </c>
+      <c r="N20" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="21">
@@ -16596,6 +16756,16 @@
           <t>NODE_S2012_13_0003</t>
         </is>
       </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>NODE_S2012_13_0023</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>NODE_S2012_13_0027</t>
+        </is>
+      </c>
       <c r="I23" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -16610,6 +16780,14 @@
         <is>
           <t>NODE_S2011_12_0022</t>
         </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>14 týmů</t>
+        </is>
+      </c>
+      <c r="N23" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -16643,6 +16821,16 @@
           <t>NODE_S2012_13_0003</t>
         </is>
       </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>NODE_S2012_13_0024</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>NODE_S2012_13_0027</t>
+        </is>
+      </c>
       <c r="I24" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -16657,6 +16845,14 @@
         <is>
           <t>NODE_S2011_12_0023</t>
         </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>střed tabulky ZČ</t>
+        </is>
+      </c>
+      <c r="N24" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="25">
@@ -16690,6 +16886,12 @@
           <t>NODE_S2012_13_0003</t>
         </is>
       </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>NODE_S2012_13_0025</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -16704,6 +16906,14 @@
         <is>
           <t>NODE_S2011_12_0024</t>
         </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>horní ZČ + postupující z předkola</t>
+        </is>
+      </c>
+      <c r="N25" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="26">
@@ -16737,6 +16947,12 @@
           <t>NODE_S2012_13_0003</t>
         </is>
       </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>NODE_S2012_13_0026</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -16751,6 +16967,14 @@
         <is>
           <t>NODE_S2011_12_0025</t>
         </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>vítězové ČF</t>
+        </is>
+      </c>
+      <c r="N26" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="27">
@@ -16784,6 +17008,8 @@
           <t>NODE_S2012_13_0003</t>
         </is>
       </c>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -16798,6 +17024,14 @@
         <is>
           <t>NODE_S2011_12_0026</t>
         </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N27" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="28">
@@ -16831,6 +17065,8 @@
           <t>NODE_S2012_13_0003</t>
         </is>
       </c>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -16845,6 +17081,14 @@
         <is>
           <t>NODE_S2011_12_0027</t>
         </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>10.–14. ZČ</t>
+        </is>
+      </c>
+      <c r="N28" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="29">
@@ -17219,6 +17463,8 @@
           <t>NODE_S2012_13_0035</t>
         </is>
       </c>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -17228,6 +17474,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>10 týmů</t>
+        </is>
+      </c>
+      <c r="N37" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -17303,6 +17557,8 @@
           <t>NODE_S2012_13_0035</t>
         </is>
       </c>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -17312,6 +17568,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>sk. o 5.–8. (horní)</t>
+        </is>
+      </c>
+      <c r="N39" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="40">
@@ -17486,6 +17750,12 @@
           <t>NODE_S2012_13_0039</t>
         </is>
       </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>NODE_S2012_13_0043</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -17500,6 +17770,14 @@
         <is>
           <t>NODE_S2011_12_0039</t>
         </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>horní polovina ZČ</t>
+        </is>
+      </c>
+      <c r="N43" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="44">
@@ -17533,6 +17811,12 @@
           <t>NODE_S2012_13_0039</t>
         </is>
       </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>NODE_S2012_13_0044</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -17547,6 +17831,14 @@
         <is>
           <t>NODE_S2011_12_0040</t>
         </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>vítězové ČF</t>
+        </is>
+      </c>
+      <c r="N44" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="45">
@@ -17580,6 +17872,8 @@
           <t>NODE_S2012_13_0039</t>
         </is>
       </c>
+      <c r="G45" t="inlineStr"/>
+      <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -17594,6 +17888,14 @@
         <is>
           <t>NODE_S2011_12_0041</t>
         </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N45" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="46">
@@ -17721,6 +18023,8 @@
           <t>NODE_S2012_13_0039</t>
         </is>
       </c>
+      <c r="G48" t="inlineStr"/>
+      <c r="H48" t="inlineStr"/>
       <c r="I48" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -17735,6 +18039,14 @@
         <is>
           <t>NODE_S2011_12_0044</t>
         </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>dolní část ZČ</t>
+        </is>
+      </c>
+      <c r="N48" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="49">
@@ -17862,6 +18174,12 @@
           <t>NODE_S2012_13_0039</t>
         </is>
       </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>NODE_S2012_13_0042</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr"/>
       <c r="I51" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -17876,6 +18194,14 @@
         <is>
           <t>NODE_S2011_12_0047</t>
         </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>horní část ZČ</t>
+        </is>
+      </c>
+      <c r="N51" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="52">
@@ -17956,6 +18282,12 @@
           <t>NODE_S2012_13_0051</t>
         </is>
       </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>NODE_S2012_13_0053</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr"/>
       <c r="I53" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -17970,6 +18302,14 @@
         <is>
           <t>NODE_S2011_12_0049</t>
         </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>16 týmů</t>
+        </is>
+      </c>
+      <c r="N53" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="54">
@@ -18003,6 +18343,8 @@
           <t>NODE_S2012_13_0051</t>
         </is>
       </c>
+      <c r="G54" t="inlineStr"/>
+      <c r="H54" t="inlineStr"/>
       <c r="I54" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -18017,6 +18359,14 @@
         <is>
           <t>NODE_S2011_12_0050</t>
         </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N54" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="55">
@@ -18050,6 +18400,12 @@
           <t>NODE_S2012_13_0051</t>
         </is>
       </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>NODE_S2012_13_0053</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr"/>
       <c r="I55" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -18064,6 +18420,14 @@
         <is>
           <t>NODE_S2011_12_0049</t>
         </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>16 týmů</t>
+        </is>
+      </c>
+      <c r="N55" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="56">
@@ -18186,6 +18550,12 @@
           <t>NODE_S2012_13_0056</t>
         </is>
       </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>NODE_S2012_13_0058</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr"/>
       <c r="I58" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -18200,6 +18570,14 @@
         <is>
           <t>NODE_S2011_12_0052</t>
         </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>12 týmů</t>
+        </is>
+      </c>
+      <c r="N58" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="59">
@@ -18233,6 +18611,8 @@
           <t>NODE_S2012_13_0056</t>
         </is>
       </c>
+      <c r="G59" t="inlineStr"/>
+      <c r="H59" t="inlineStr"/>
       <c r="I59" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -18247,6 +18627,14 @@
         <is>
           <t>NODE_S2011_12_0053</t>
         </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N59" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="60">
@@ -18327,6 +18715,12 @@
           <t>NODE_S2012_13_0059</t>
         </is>
       </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>NODE_S2012_13_0061</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr"/>
       <c r="I61" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -18336,6 +18730,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>8 týmů</t>
+        </is>
+      </c>
+      <c r="N61" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="62">
@@ -18369,6 +18771,8 @@
           <t>NODE_S2012_13_0059</t>
         </is>
       </c>
+      <c r="G62" t="inlineStr"/>
+      <c r="H62" t="inlineStr"/>
       <c r="I62" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -18378,6 +18782,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N62" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="63">
@@ -18458,6 +18870,8 @@
           <t>NODE_S2012_13_0059</t>
         </is>
       </c>
+      <c r="G64" t="inlineStr"/>
+      <c r="H64" t="inlineStr"/>
       <c r="I64" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -18467,6 +18881,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N64" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="65">
@@ -18547,6 +18969,8 @@
           <t>NODE_S2012_13_0059</t>
         </is>
       </c>
+      <c r="G66" t="inlineStr"/>
+      <c r="H66" t="inlineStr"/>
       <c r="I66" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -18556,6 +18980,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N66" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="67">
@@ -18636,6 +19068,8 @@
           <t>NODE_S2012_13_0059</t>
         </is>
       </c>
+      <c r="G68" t="inlineStr"/>
+      <c r="H68" t="inlineStr"/>
       <c r="I68" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -18645,6 +19079,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N68" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="69">
@@ -18725,6 +19167,8 @@
           <t>NODE_S2012_13_0059</t>
         </is>
       </c>
+      <c r="G70" t="inlineStr"/>
+      <c r="H70" t="inlineStr"/>
       <c r="I70" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -18734,6 +19178,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N70" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="71">
@@ -18814,6 +19266,12 @@
           <t>NODE_S2012_13_0070</t>
         </is>
       </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>NODE_S2012_13_0072</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr"/>
       <c r="I72" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -18823,6 +19281,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>6 týmů</t>
+        </is>
+      </c>
+      <c r="N72" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="73">
@@ -18856,6 +19322,8 @@
           <t>NODE_S2012_13_0070</t>
         </is>
       </c>
+      <c r="G73" t="inlineStr"/>
+      <c r="H73" t="inlineStr"/>
       <c r="I73" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -18870,6 +19338,14 @@
         <is>
           <t>NODE_S2011_12_0066</t>
         </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N73" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="74">
@@ -18903,6 +19379,8 @@
           <t>NODE_S2012_13_0070</t>
         </is>
       </c>
+      <c r="G74" t="inlineStr"/>
+      <c r="H74" t="inlineStr"/>
       <c r="I74" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -18917,6 +19395,14 @@
         <is>
           <t>NODE_S2011_12_0066</t>
         </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N74" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="75">
@@ -19039,6 +19525,12 @@
           <t>NODE_S2012_13_0075</t>
         </is>
       </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>NODE_S2012_13_0077</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr"/>
       <c r="I77" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -19048,6 +19540,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>5 týmů</t>
+        </is>
+      </c>
+      <c r="N77" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="78">
@@ -19081,6 +19581,8 @@
           <t>NODE_S2012_13_0075</t>
         </is>
       </c>
+      <c r="G78" t="inlineStr"/>
+      <c r="H78" t="inlineStr"/>
       <c r="I78" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -19090,6 +19592,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N78" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="79">
@@ -19170,6 +19680,12 @@
           <t>NODE_S2012_13_0078</t>
         </is>
       </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>NODE_S2012_13_0081</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr"/>
       <c r="I80" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -19184,6 +19700,14 @@
         <is>
           <t>NODE_S2011_12_0069</t>
         </is>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>13 týmů</t>
+        </is>
+      </c>
+      <c r="N80" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="81">
@@ -19217,6 +19741,8 @@
           <t>NODE_S2012_13_0078</t>
         </is>
       </c>
+      <c r="G81" t="inlineStr"/>
+      <c r="H81" t="inlineStr"/>
       <c r="I81" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -19226,6 +19752,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>poražení SF</t>
+        </is>
+      </c>
+      <c r="N81" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="82">
@@ -19259,6 +19793,8 @@
           <t>NODE_S2012_13_0078</t>
         </is>
       </c>
+      <c r="G82" t="inlineStr"/>
+      <c r="H82" t="inlineStr"/>
       <c r="I82" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -19268,6 +19804,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N82" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="83">
@@ -19642,6 +20186,8 @@
           <t>NODE_S2012_13_0082</t>
         </is>
       </c>
+      <c r="G91" t="inlineStr"/>
+      <c r="H91" t="inlineStr"/>
       <c r="I91" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -19651,6 +20197,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N91" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="92">
@@ -19684,6 +20238,8 @@
           <t>NODE_S2012_13_0082</t>
         </is>
       </c>
+      <c r="G92" t="inlineStr"/>
+      <c r="H92" t="inlineStr"/>
       <c r="I92" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -19693,6 +20249,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N92" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="93">
@@ -19862,6 +20426,12 @@
           <t>NODE_S2012_13_0093</t>
         </is>
       </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>NODE_S2012_13_0096</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr"/>
       <c r="I96" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -19876,6 +20446,14 @@
         <is>
           <t>NODE_S2011_12_0080</t>
         </is>
+      </c>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>13 týmů</t>
+        </is>
+      </c>
+      <c r="N96" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="97">
@@ -19909,6 +20487,8 @@
           <t>NODE_S2012_13_0093</t>
         </is>
       </c>
+      <c r="G97" t="inlineStr"/>
+      <c r="H97" t="inlineStr"/>
       <c r="I97" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -19918,6 +20498,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N97" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="98">
@@ -19951,6 +20539,8 @@
           <t>NODE_S2012_13_0093</t>
         </is>
       </c>
+      <c r="G98" t="inlineStr"/>
+      <c r="H98" t="inlineStr"/>
       <c r="I98" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -19960,6 +20550,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N98" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="99">
@@ -20040,6 +20638,12 @@
           <t>NODE_S2012_13_0098</t>
         </is>
       </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>NODE_S2012_13_0100</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr"/>
       <c r="I100" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -20054,6 +20658,14 @@
         <is>
           <t>NODE_S2011_12_0084</t>
         </is>
+      </c>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>11 týmů</t>
+        </is>
+      </c>
+      <c r="N100" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="101">
@@ -20087,6 +20699,8 @@
           <t>NODE_S2012_13_0098</t>
         </is>
       </c>
+      <c r="G101" t="inlineStr"/>
+      <c r="H101" t="inlineStr"/>
       <c r="I101" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -20102,7 +20716,17 @@
           <t>NODE_S2011_12_0085</t>
         </is>
       </c>
-    </row>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N101" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="102"/>
+    <row r="103"/>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
@@ -20232,6 +20856,7 @@
         </is>
       </c>
     </row>
+    <row r="111"/>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>

--- a/data/S2012_13_FINAL.xlsx
+++ b/data/S2012_13_FINAL.xlsx
@@ -912,6 +912,11 @@
           <t>HC Škoda Plzeň (C)</t>
         </is>
       </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
       <c r="F7" t="n">
         <v>52</v>
       </c>
@@ -16198,8 +16203,6 @@
           <t>NODE_S2012_13_0007</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -16255,8 +16258,6 @@
           <t>NODE_S2012_13_0007</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -16312,8 +16313,6 @@
           <t>NODE_S2012_13_0007</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -16369,8 +16368,6 @@
           <t>NODE_S2012_13_0007</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -16426,8 +16423,6 @@
           <t>NODE_S2012_13_0001</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -16483,8 +16478,6 @@
           <t>NODE_S2012_13_0007</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -16540,8 +16533,6 @@
           <t>NODE_S2012_13_0007</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -16891,7 +16882,6 @@
           <t>NODE_S2012_13_0025</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -16952,7 +16942,6 @@
           <t>NODE_S2012_13_0026</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -17008,8 +16997,6 @@
           <t>NODE_S2012_13_0003</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -17065,8 +17052,6 @@
           <t>NODE_S2012_13_0003</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -17463,8 +17448,6 @@
           <t>NODE_S2012_13_0035</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr"/>
-      <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -17557,8 +17540,6 @@
           <t>NODE_S2012_13_0035</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr"/>
-      <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -17755,7 +17736,6 @@
           <t>NODE_S2012_13_0043</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -17816,7 +17796,6 @@
           <t>NODE_S2012_13_0044</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -17872,8 +17851,6 @@
           <t>NODE_S2012_13_0039</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr"/>
-      <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -18023,8 +18000,6 @@
           <t>NODE_S2012_13_0039</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr"/>
-      <c r="H48" t="inlineStr"/>
       <c r="I48" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -18179,7 +18154,6 @@
           <t>NODE_S2012_13_0042</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr"/>
       <c r="I51" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -18287,7 +18261,6 @@
           <t>NODE_S2012_13_0053</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr"/>
       <c r="I53" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -18343,8 +18316,6 @@
           <t>NODE_S2012_13_0051</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr"/>
-      <c r="H54" t="inlineStr"/>
       <c r="I54" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -18405,7 +18376,6 @@
           <t>NODE_S2012_13_0053</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr"/>
       <c r="I55" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -18555,7 +18525,6 @@
           <t>NODE_S2012_13_0058</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr"/>
       <c r="I58" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -18611,8 +18580,6 @@
           <t>NODE_S2012_13_0056</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr"/>
-      <c r="H59" t="inlineStr"/>
       <c r="I59" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -18720,7 +18687,6 @@
           <t>NODE_S2012_13_0061</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr"/>
       <c r="I61" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -18771,8 +18737,6 @@
           <t>NODE_S2012_13_0059</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr"/>
-      <c r="H62" t="inlineStr"/>
       <c r="I62" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -18870,8 +18834,6 @@
           <t>NODE_S2012_13_0059</t>
         </is>
       </c>
-      <c r="G64" t="inlineStr"/>
-      <c r="H64" t="inlineStr"/>
       <c r="I64" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -18969,8 +18931,6 @@
           <t>NODE_S2012_13_0059</t>
         </is>
       </c>
-      <c r="G66" t="inlineStr"/>
-      <c r="H66" t="inlineStr"/>
       <c r="I66" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -19068,8 +19028,6 @@
           <t>NODE_S2012_13_0059</t>
         </is>
       </c>
-      <c r="G68" t="inlineStr"/>
-      <c r="H68" t="inlineStr"/>
       <c r="I68" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -19167,8 +19125,6 @@
           <t>NODE_S2012_13_0059</t>
         </is>
       </c>
-      <c r="G70" t="inlineStr"/>
-      <c r="H70" t="inlineStr"/>
       <c r="I70" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -19271,7 +19227,6 @@
           <t>NODE_S2012_13_0072</t>
         </is>
       </c>
-      <c r="H72" t="inlineStr"/>
       <c r="I72" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -19322,8 +19277,6 @@
           <t>NODE_S2012_13_0070</t>
         </is>
       </c>
-      <c r="G73" t="inlineStr"/>
-      <c r="H73" t="inlineStr"/>
       <c r="I73" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -19379,8 +19332,6 @@
           <t>NODE_S2012_13_0070</t>
         </is>
       </c>
-      <c r="G74" t="inlineStr"/>
-      <c r="H74" t="inlineStr"/>
       <c r="I74" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -19530,7 +19481,6 @@
           <t>NODE_S2012_13_0077</t>
         </is>
       </c>
-      <c r="H77" t="inlineStr"/>
       <c r="I77" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -19581,8 +19531,6 @@
           <t>NODE_S2012_13_0075</t>
         </is>
       </c>
-      <c r="G78" t="inlineStr"/>
-      <c r="H78" t="inlineStr"/>
       <c r="I78" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -19685,7 +19633,6 @@
           <t>NODE_S2012_13_0081</t>
         </is>
       </c>
-      <c r="H80" t="inlineStr"/>
       <c r="I80" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -19741,8 +19688,6 @@
           <t>NODE_S2012_13_0078</t>
         </is>
       </c>
-      <c r="G81" t="inlineStr"/>
-      <c r="H81" t="inlineStr"/>
       <c r="I81" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -19793,8 +19738,6 @@
           <t>NODE_S2012_13_0078</t>
         </is>
       </c>
-      <c r="G82" t="inlineStr"/>
-      <c r="H82" t="inlineStr"/>
       <c r="I82" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -20186,8 +20129,6 @@
           <t>NODE_S2012_13_0082</t>
         </is>
       </c>
-      <c r="G91" t="inlineStr"/>
-      <c r="H91" t="inlineStr"/>
       <c r="I91" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -20238,8 +20179,6 @@
           <t>NODE_S2012_13_0082</t>
         </is>
       </c>
-      <c r="G92" t="inlineStr"/>
-      <c r="H92" t="inlineStr"/>
       <c r="I92" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -20431,7 +20370,6 @@
           <t>NODE_S2012_13_0096</t>
         </is>
       </c>
-      <c r="H96" t="inlineStr"/>
       <c r="I96" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -20487,8 +20425,6 @@
           <t>NODE_S2012_13_0093</t>
         </is>
       </c>
-      <c r="G97" t="inlineStr"/>
-      <c r="H97" t="inlineStr"/>
       <c r="I97" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -20539,8 +20475,6 @@
           <t>NODE_S2012_13_0093</t>
         </is>
       </c>
-      <c r="G98" t="inlineStr"/>
-      <c r="H98" t="inlineStr"/>
       <c r="I98" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -20643,7 +20577,6 @@
           <t>NODE_S2012_13_0100</t>
         </is>
       </c>
-      <c r="H100" t="inlineStr"/>
       <c r="I100" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -20699,8 +20632,6 @@
           <t>NODE_S2012_13_0098</t>
         </is>
       </c>
-      <c r="G101" t="inlineStr"/>
-      <c r="H101" t="inlineStr"/>
       <c r="I101" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -20725,8 +20656,6 @@
         <v>5</v>
       </c>
     </row>
-    <row r="102"/>
-    <row r="103"/>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
@@ -20856,7 +20785,6 @@
         </is>
       </c>
     </row>
-    <row r="111"/>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
@@ -37032,7 +36960,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B18"/>
+  <dimension ref="A1:B19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -37248,6 +37176,18 @@
       <c r="B18" t="inlineStr">
         <is>
           <t>0 oprav kvalifikačních levelů. Sloupec Q (level) aktualizován.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>mistr</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>HC Škoda Plzeň</t>
         </is>
       </c>
     </row>

--- a/data/S2012_13_FINAL.xlsx
+++ b/data/S2012_13_FINAL.xlsx
@@ -20656,6 +20656,8 @@
         <v>5</v>
       </c>
     </row>
+    <row r="102"/>
+    <row r="103"/>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
@@ -20785,6 +20787,7 @@
         </is>
       </c>
     </row>
+    <row r="111"/>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>

--- a/data/S2012_13_FINAL.xlsx
+++ b/data/S2012_13_FINAL.xlsx
@@ -7087,7 +7087,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W62"/>
+  <dimension ref="A1:W74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -10801,6 +10801,500 @@
       <c r="V62" t="inlineStr">
         <is>
           <t>SER_S2012_13_0079</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Krajská liga</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>NODE_S2012_13_0103</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>1</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>HC Světlá nad Sázavou</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>Krajská liga</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>NODE_S2012_13_0103</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q64" t="inlineStr">
+        <is>
+          <t>CLUB_S2012_13_0278</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>TR_S2012_13_00353</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Ústí nad Orlicí</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>NODE_S2012_13_0104</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>1</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Sokol Čestice</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>Ústí nad Orlicí</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>NODE_S2012_13_0104</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q66" t="inlineStr">
+        <is>
+          <t>CLUB_S2012_13_0279</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>TR_S2012_13_00354</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>2</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>SK Žamberk</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>Ústí nad Orlicí</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>NODE_S2012_13_0104</t>
+        </is>
+      </c>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q67" t="inlineStr">
+        <is>
+          <t>CLUB_S2012_13_0280</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>TR_S2012_13_00355</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>3</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>SK Třebechovice pod Orebem B</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>Ústí nad Orlicí</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>NODE_S2012_13_0104</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q68" t="inlineStr">
+        <is>
+          <t>CLUB_S2012_13_0281</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>TR_S2012_13_00356</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>4</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Sokol Řetová</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>Ústí nad Orlicí</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>NODE_S2012_13_0104</t>
+        </is>
+      </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q69" t="inlineStr">
+        <is>
+          <t>CLUB_S2012_13_0282</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>TR_S2012_13_00357</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>5</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>TJ Voděrady</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>Ústí nad Orlicí</t>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>NODE_S2012_13_0104</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q70" t="inlineStr">
+        <is>
+          <t>CLUB_S2012_13_0283</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>TR_S2012_13_00358</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>6</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>TJ Jiskra Králíky</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>Ústí nad Orlicí</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>NODE_S2012_13_0104</t>
+        </is>
+      </c>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q71" t="inlineStr">
+        <is>
+          <t>CLUB_S2012_13_0284</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>TR_S2012_13_00359</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>7</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>HC Dlouhoňovice</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>Ústí nad Orlicí</t>
+        </is>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>NODE_S2012_13_0104</t>
+        </is>
+      </c>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q72" t="inlineStr">
+        <is>
+          <t>CLUB_S2012_13_0285</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>TR_S2012_13_00360</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>8</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>HC Město Rychnov nad Kněžnou</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>Ústí nad Orlicí</t>
+        </is>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>NODE_S2012_13_0104</t>
+        </is>
+      </c>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q73" t="inlineStr">
+        <is>
+          <t>CLUB_S2012_13_0286</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>TR_S2012_13_00361</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>9</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>TJ Lanškroun "B"</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>Ústí nad Orlicí</t>
+        </is>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>NODE_S2012_13_0104</t>
+        </is>
+      </c>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q74" t="inlineStr">
+        <is>
+          <t>CLUB_S2012_13_0287</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>TR_S2012_13_00362</t>
         </is>
       </c>
     </row>
@@ -15503,7 +15997,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N115"/>
+  <dimension ref="A1:N119"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20813,6 +21307,124 @@
       <c r="A115" t="inlineStr">
         <is>
           <t>II.liga: Západ/Střed/Východ + 8F/QF/SF/finále.</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>NODE_S2012_13_0101</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Praha – Pražský přebor</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>league</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy).</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>NODE_S2012_13_0102</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Plzeňský – Domažlice</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>league</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>REG_PLK</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>NODE_S2012_13_0059</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy).</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>NODE_S2012_13_0103</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Pardubický – Krajská liga</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>league</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy).</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>NODE_S2012_13_0104</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Pardubický – Ústí nad Orlicí</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>league</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy).</t>
         </is>
       </c>
     </row>
@@ -26531,7 +27143,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J245"/>
+  <dimension ref="A1:J266"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="10" max="10"/>
@@ -36949,6 +37561,678 @@
       <c r="J245" t="inlineStr">
         <is>
           <t>Havlíčkův Brod</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>CLUB_S2012_13_0267</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>HC Roudnice nad Labem</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>HC Roudnice nad Labem</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>30PRAH</t>
+        </is>
+      </c>
+      <c r="F246" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I246" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>CLUB_S2012_13_0268</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>SK Černošice Tygři</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>SK Černošice Tygři</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>30PRAH</t>
+        </is>
+      </c>
+      <c r="F247" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I247" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>CLUB_S2012_13_0269</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>Katovice</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>Katovice</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>30PLZN</t>
+        </is>
+      </c>
+      <c r="F248" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I248" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>CLUB_S2012_13_0270</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>Horažďovice</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>Horažďovice</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>30PLZN</t>
+        </is>
+      </c>
+      <c r="F249" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I249" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>CLUB_S2012_13_0271</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>Cehnice</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>Cehnice</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>30PLZN</t>
+        </is>
+      </c>
+      <c r="F250" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I250" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>CLUB_S2012_13_0272</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>TJ Start Luby</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>TJ Start Luby</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>30PLZN</t>
+        </is>
+      </c>
+      <c r="F251" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I251" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>CLUB_S2012_13_0273</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>Drahonice</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>Drahonice</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>30PLZN</t>
+        </is>
+      </c>
+      <c r="F252" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I252" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>CLUB_S2012_13_0274</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>Sušice</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>Sušice</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>30PLZN</t>
+        </is>
+      </c>
+      <c r="F253" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I253" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>CLUB_S2012_13_0275</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>finále</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>finále</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>30PLZN</t>
+        </is>
+      </c>
+      <c r="F254" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I254" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>CLUB_S2012_13_0276</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>SD-CHO 6:6,4:6</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>SD-CHO 6:6,4:6</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>30PLZN</t>
+        </is>
+      </c>
+      <c r="F255" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I255" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>CLUB_S2012_13_0277</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>finále: Dvůr-Týniště 7:2</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>finále: Dvůr-Týniště 7:2</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>30PLZN</t>
+        </is>
+      </c>
+      <c r="F256" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I256" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>CLUB_S2012_13_0278</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>HC Světlá nad Sázavou</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>HC Světlá nad Sázavou</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>30PARD</t>
+        </is>
+      </c>
+      <c r="F257" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I257" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>CLUB_S2012_13_0279</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>Sokol Čestice</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>Sokol Čestice</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>30PARD</t>
+        </is>
+      </c>
+      <c r="F258" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I258" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>CLUB_S2012_13_0280</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>SK Žamberk</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>SK Žamberk</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>30PARD</t>
+        </is>
+      </c>
+      <c r="F259" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I259" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>CLUB_S2012_13_0281</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>SK Třebechovice pod Orebem B</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>SK Třebechovice pod Orebem B</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>30PARD</t>
+        </is>
+      </c>
+      <c r="F260" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I260" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>CLUB_S2012_13_0282</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>Sokol Řetová</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>Sokol Řetová</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>30PARD</t>
+        </is>
+      </c>
+      <c r="F261" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I261" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>CLUB_S2012_13_0283</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>TJ Voděrady</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>TJ Voděrady</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>30PARD</t>
+        </is>
+      </c>
+      <c r="F262" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I262" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>CLUB_S2012_13_0284</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>TJ Jiskra Králíky</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>TJ Jiskra Králíky</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>30PARD</t>
+        </is>
+      </c>
+      <c r="F263" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I263" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>CLUB_S2012_13_0285</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>HC Dlouhoňovice</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>HC Dlouhoňovice</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>30PARD</t>
+        </is>
+      </c>
+      <c r="F264" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I264" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>CLUB_S2012_13_0286</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>HC Město Rychnov nad Kněžnou</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>HC Město Rychnov nad Kněžnou</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>30PARD</t>
+        </is>
+      </c>
+      <c r="F265" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I265" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>CLUB_S2012_13_0287</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>TJ Lanškroun "B"</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>TJ Lanškroun "B"</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>30PARD</t>
+        </is>
+      </c>
+      <c r="F266" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="I266" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy, bez statistik).</t>
         </is>
       </c>
     </row>
@@ -42709,7 +43993,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W29"/>
+  <dimension ref="A1:W32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -44779,6 +46063,118 @@
       <c r="U29" s="2" t="n"/>
       <c r="V29" s="2" t="n"/>
       <c r="W29" s="2" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Pražský přebor</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>NODE_S2012_13_0101</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>7</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>HC Roudnice nad Labem</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>Pražský přebor</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>NODE_S2012_13_0101</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>CLUB_S2012_13_0267</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>TR_S2012_13_00342</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>10</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>SK Černošice Tygři</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>Pražský přebor</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>NODE_S2012_13_0101</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>CLUB_S2012_13_0268</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>TR_S2012_13_00343</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -49204,7 +50600,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W126"/>
+  <dimension ref="A1:W136"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -56571,6 +57967,424 @@
       <c r="V126" t="inlineStr">
         <is>
           <t>TR_S2012_13_00219</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Domažlice</t>
+        </is>
+      </c>
+      <c r="O127" t="inlineStr">
+        <is>
+          <t>NODE_S2012_13_0102</t>
+        </is>
+      </c>
+      <c r="P127" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C128" t="n">
+        <v>1</v>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>Katovice</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N128" t="inlineStr">
+        <is>
+          <t>Domažlice</t>
+        </is>
+      </c>
+      <c r="O128" t="inlineStr">
+        <is>
+          <t>NODE_S2012_13_0102</t>
+        </is>
+      </c>
+      <c r="P128" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q128" t="inlineStr">
+        <is>
+          <t>CLUB_S2012_13_0269</t>
+        </is>
+      </c>
+      <c r="V128" t="inlineStr">
+        <is>
+          <t>TR_S2012_13_00344</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C129" t="n">
+        <v>2</v>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>Horažďovice</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N129" t="inlineStr">
+        <is>
+          <t>Domažlice</t>
+        </is>
+      </c>
+      <c r="O129" t="inlineStr">
+        <is>
+          <t>NODE_S2012_13_0102</t>
+        </is>
+      </c>
+      <c r="P129" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q129" t="inlineStr">
+        <is>
+          <t>CLUB_S2012_13_0270</t>
+        </is>
+      </c>
+      <c r="V129" t="inlineStr">
+        <is>
+          <t>TR_S2012_13_00345</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C130" t="n">
+        <v>3</v>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>Cehnice</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N130" t="inlineStr">
+        <is>
+          <t>Domažlice</t>
+        </is>
+      </c>
+      <c r="O130" t="inlineStr">
+        <is>
+          <t>NODE_S2012_13_0102</t>
+        </is>
+      </c>
+      <c r="P130" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q130" t="inlineStr">
+        <is>
+          <t>CLUB_S2012_13_0271</t>
+        </is>
+      </c>
+      <c r="V130" t="inlineStr">
+        <is>
+          <t>TR_S2012_13_00346</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C131" t="n">
+        <v>4</v>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>TJ Start Luby</t>
+        </is>
+      </c>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N131" t="inlineStr">
+        <is>
+          <t>Domažlice</t>
+        </is>
+      </c>
+      <c r="O131" t="inlineStr">
+        <is>
+          <t>NODE_S2012_13_0102</t>
+        </is>
+      </c>
+      <c r="P131" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q131" t="inlineStr">
+        <is>
+          <t>CLUB_S2012_13_0272</t>
+        </is>
+      </c>
+      <c r="V131" t="inlineStr">
+        <is>
+          <t>TR_S2012_13_00347</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C132" t="n">
+        <v>5</v>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>Drahonice</t>
+        </is>
+      </c>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N132" t="inlineStr">
+        <is>
+          <t>Domažlice</t>
+        </is>
+      </c>
+      <c r="O132" t="inlineStr">
+        <is>
+          <t>NODE_S2012_13_0102</t>
+        </is>
+      </c>
+      <c r="P132" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q132" t="inlineStr">
+        <is>
+          <t>CLUB_S2012_13_0273</t>
+        </is>
+      </c>
+      <c r="V132" t="inlineStr">
+        <is>
+          <t>TR_S2012_13_00348</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C133" t="n">
+        <v>6</v>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>Sušice</t>
+        </is>
+      </c>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N133" t="inlineStr">
+        <is>
+          <t>Domažlice</t>
+        </is>
+      </c>
+      <c r="O133" t="inlineStr">
+        <is>
+          <t>NODE_S2012_13_0102</t>
+        </is>
+      </c>
+      <c r="P133" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q133" t="inlineStr">
+        <is>
+          <t>CLUB_S2012_13_0274</t>
+        </is>
+      </c>
+      <c r="V133" t="inlineStr">
+        <is>
+          <t>TR_S2012_13_00349</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>finále</t>
+        </is>
+      </c>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N134" t="inlineStr">
+        <is>
+          <t>Domažlice</t>
+        </is>
+      </c>
+      <c r="O134" t="inlineStr">
+        <is>
+          <t>NODE_S2012_13_0102</t>
+        </is>
+      </c>
+      <c r="P134" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q134" t="inlineStr">
+        <is>
+          <t>CLUB_S2012_13_0275</t>
+        </is>
+      </c>
+      <c r="V134" t="inlineStr">
+        <is>
+          <t>TR_S2012_13_00350</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>SD-CHO 6:6,4:6</t>
+        </is>
+      </c>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N135" t="inlineStr">
+        <is>
+          <t>Domažlice</t>
+        </is>
+      </c>
+      <c r="O135" t="inlineStr">
+        <is>
+          <t>NODE_S2012_13_0102</t>
+        </is>
+      </c>
+      <c r="P135" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q135" t="inlineStr">
+        <is>
+          <t>CLUB_S2012_13_0276</t>
+        </is>
+      </c>
+      <c r="V135" t="inlineStr">
+        <is>
+          <t>TR_S2012_13_00351</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>finále: Dvůr-Týniště 7:2</t>
+        </is>
+      </c>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N136" t="inlineStr">
+        <is>
+          <t>Domažlice</t>
+        </is>
+      </c>
+      <c r="O136" t="inlineStr">
+        <is>
+          <t>NODE_S2012_13_0102</t>
+        </is>
+      </c>
+      <c r="P136" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q136" t="inlineStr">
+        <is>
+          <t>CLUB_S2012_13_0277</t>
+        </is>
+      </c>
+      <c r="V136" t="inlineStr">
+        <is>
+          <t>TR_S2012_13_00352</t>
         </is>
       </c>
     </row>

--- a/data/S2012_13_FINAL.xlsx
+++ b/data/S2012_13_FINAL.xlsx
@@ -41,7 +41,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -60,8 +60,12 @@
       <b val="1"/>
       <color rgb="00FFFFFF"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00B45309"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -83,6 +87,11 @@
         <fgColor rgb="00305496"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFE0B2"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -96,7 +105,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -107,6 +116,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -21150,8 +21161,6 @@
         <v>5</v>
       </c>
     </row>
-    <row r="102"/>
-    <row r="103"/>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
@@ -21281,7 +21290,6 @@
         </is>
       </c>
     </row>
-    <row r="111"/>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
@@ -38489,7 +38497,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F38"/>
+  <dimension ref="A1:F44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -38546,7 +38554,7 @@
           <t>CLUB_S2012_13_0004</t>
         </is>
       </c>
-      <c r="D2" s="5" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -38566,7 +38574,7 @@
           <t>CLUB_S2012_13_0014</t>
         </is>
       </c>
-      <c r="D3" s="5" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>TBD: city 'KLH VT VTJ Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -38586,7 +38594,7 @@
           <t>CLUB_S2012_13_0021</t>
         </is>
       </c>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>TBD: city 'Sportovní klub Kadaň' → 'Kadaň' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -38606,7 +38614,7 @@
           <t>CLUB_S2012_13_0032</t>
         </is>
       </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>TBD: city 'VSK Technika Brno' → 'Technika Brno' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -38626,7 +38634,7 @@
           <t>CLUB_S2012_13_0035</t>
         </is>
       </c>
-      <c r="D6" s="5" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
         </is>
@@ -38646,7 +38654,7 @@
           <t>CLUB_S2012_13_0039</t>
         </is>
       </c>
-      <c r="D7" s="5" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -38666,7 +38674,7 @@
           <t>CLUB_S2012_13_0057</t>
         </is>
       </c>
-      <c r="D8" s="5" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>TBD: city 'SHC Maso Brejcha Klatovy' → 'Klatovy' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -38686,7 +38694,7 @@
           <t>CLUB_S2012_13_0058</t>
         </is>
       </c>
-      <c r="D9" s="5" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
@@ -38706,7 +38714,7 @@
           <t>CLUB_S2012_13_0061</t>
         </is>
       </c>
-      <c r="D10" s="5" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>TBD: city 'Vlci Jablonec nad Nisou' → 'Jablonec nad Nisou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -38726,7 +38734,7 @@
           <t>CLUB_S2012_13_0068</t>
         </is>
       </c>
-      <c r="D11" s="5" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>TBD: city 'NED Hockey Nymburk' → 'Nymburk' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -38746,7 +38754,7 @@
           <t>CLUB_S2012_13_0070</t>
         </is>
       </c>
-      <c r="D12" s="5" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
         </is>
@@ -38766,7 +38774,7 @@
           <t>CLUB_S2012_13_0072</t>
         </is>
       </c>
-      <c r="D13" s="5" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -38786,7 +38794,7 @@
           <t>CLUB_S2012_13_0073</t>
         </is>
       </c>
-      <c r="D14" s="5" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
         </is>
@@ -38806,7 +38814,7 @@
           <t>CLUB_S2012_13_0077</t>
         </is>
       </c>
-      <c r="D15" s="5" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>TBD: city 'RT Torax Poruba' → 'Poruba' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -38826,7 +38834,7 @@
           <t>CLUB_S2012_13_0089</t>
         </is>
       </c>
-      <c r="D16" s="5" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>TBD: city 'UHK LEV Slaný' → 'Slaný' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -38846,7 +38854,7 @@
           <t>CLUB_S2012_13_0092</t>
         </is>
       </c>
-      <c r="D17" s="5" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
         </is>
@@ -38866,7 +38874,7 @@
           <t>CLUB_S2012_13_0107</t>
         </is>
       </c>
-      <c r="D18" s="5" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -38886,7 +38894,7 @@
           <t>CLUB_S2012_13_0116</t>
         </is>
       </c>
-      <c r="D19" s="5" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -38906,7 +38914,7 @@
           <t>CLUB_S2012_13_0148</t>
         </is>
       </c>
-      <c r="D20" s="5" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>TBD: city 'SKP Rapid Plzeň' → 'Plzeň' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -38926,7 +38934,7 @@
           <t>CLUB_S2012_13_0156</t>
         </is>
       </c>
-      <c r="D21" s="5" t="inlineStr">
+      <c r="D21" t="inlineStr">
         <is>
           <t>TBD: city 'Ekonomické Stavby Plzeň' → 'Plzeň' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -38946,7 +38954,7 @@
           <t>CLUB_S2012_13_0170</t>
         </is>
       </c>
-      <c r="D22" s="5" t="inlineStr">
+      <c r="D22" t="inlineStr">
         <is>
           <t>TBD: extrahováno z block_name: 'HC Dolní Kamenice — odstoupila' [fix_club_notes_in_block_name]</t>
         </is>
@@ -38966,7 +38974,7 @@
           <t>CLUB_S2012_13_0175</t>
         </is>
       </c>
-      <c r="D23" s="5" t="inlineStr">
+      <c r="D23" t="inlineStr">
         <is>
           <t>TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
         </is>
@@ -38986,7 +38994,7 @@
           <t>CLUB_S2012_13_0189</t>
         </is>
       </c>
-      <c r="D24" s="5" t="inlineStr">
+      <c r="D24" t="inlineStr">
         <is>
           <t>TBD: city 'IHT Brimstones Cheb' → 'Cheb' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -39006,7 +39014,7 @@
           <t>CLUB_S2012_13_0191</t>
         </is>
       </c>
-      <c r="D25" s="5" t="inlineStr">
+      <c r="D25" t="inlineStr">
         <is>
           <t>TBD: city 'PSK 96 Cheb' → 'Cheb' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -39026,7 +39034,7 @@
           <t>CLUB_S2012_13_0205</t>
         </is>
       </c>
-      <c r="D26" s="5" t="inlineStr">
+      <c r="D26" t="inlineStr">
         <is>
           <t>TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
         </is>
@@ -39046,7 +39054,7 @@
           <t>CLUB_S2012_13_0206</t>
         </is>
       </c>
-      <c r="D27" s="5" t="inlineStr">
+      <c r="D27" t="inlineStr">
         <is>
           <t>TBD: city 'BK JTC Nová Paka' → 'Nová Paka' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -39066,7 +39074,7 @@
           <t>CLUB_S2012_13_0208</t>
         </is>
       </c>
-      <c r="D28" s="5" t="inlineStr">
+      <c r="D28" t="inlineStr">
         <is>
           <t>TBD: city 'Stadion Nový Bydžov' → 'Nový Bydžov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -39086,7 +39094,7 @@
           <t>CLUB_S2012_13_0221</t>
         </is>
       </c>
-      <c r="D29" s="5" t="inlineStr">
+      <c r="D29" t="inlineStr">
         <is>
           <t>TBD: city 'Závodní hokejové Pardubice' → 'Pardubice' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -39106,7 +39114,7 @@
           <t>CLUB_S2012_13_0222</t>
         </is>
       </c>
-      <c r="D30" s="5" t="inlineStr">
+      <c r="D30" t="inlineStr">
         <is>
           <t>TBD: K ověření, zda jde o B-tým nebo samostatný klub (Česká Třebová mohla mít dva různé kluby). Smart fix prev: 0650 (Sokol Česká Třebová = jiný klub) → 0656 (Perla II z 49/50 = B-tým Perly). Audit 04/2026.</t>
         </is>
@@ -39126,7 +39134,7 @@
           <t>CLUB_S2012_13_0223</t>
         </is>
       </c>
-      <c r="D31" s="5" t="inlineStr">
+      <c r="D31" t="inlineStr">
         <is>
           <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
         </is>
@@ -39146,7 +39154,7 @@
           <t>CLUB_S2012_13_0235</t>
         </is>
       </c>
-      <c r="D32" s="5" t="inlineStr">
+      <c r="D32" t="inlineStr">
         <is>
           <t>TBD: auto-prev_club_id doplnění → CLUB_S2011_12_0063 (weak, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
@@ -39166,7 +39174,7 @@
           <t>CLUB_S2012_13_0243</t>
         </is>
       </c>
-      <c r="D33" s="5" t="inlineStr">
+      <c r="D33" t="inlineStr">
         <is>
           <t>TBD: city 'HCM Warrior Brno' → 'Brno' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -39186,7 +39194,7 @@
           <t>CLUB_S2012_13_0259</t>
         </is>
       </c>
-      <c r="D34" s="5" t="inlineStr">
+      <c r="D34" t="inlineStr">
         <is>
           <t>TBD: city 'RT Torax Poruba' → 'Poruba' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -39206,7 +39214,7 @@
           <t>CLUB_S2012_13_0261</t>
         </is>
       </c>
-      <c r="D35" s="5" t="inlineStr">
+      <c r="D35" t="inlineStr">
         <is>
           <t>TBD: auto-prev_club_id doplnění → CLUB_S2011_12_0067 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
@@ -39226,7 +39234,7 @@
           <t>NODE_S2012_13_0030</t>
         </is>
       </c>
-      <c r="D36" s="5" t="inlineStr">
+      <c r="D36" t="inlineStr">
         <is>
           <t>top-level kvalifikace bez feeds_into: 'KVAL  skupina A'</t>
         </is>
@@ -39246,7 +39254,7 @@
           <t>NODE_S2012_13_0031</t>
         </is>
       </c>
-      <c r="D37" s="5" t="inlineStr">
+      <c r="D37" t="inlineStr">
         <is>
           <t>top-level kvalifikace bez feeds_into: 'KVAL  skupina B'</t>
         </is>
@@ -39266,11 +39274,167 @@
           <t>NODE_S2012_13_0032</t>
         </is>
       </c>
-      <c r="D38" s="5" t="inlineStr">
+      <c r="D38" t="inlineStr">
         <is>
           <t>top-level kvalifikace bez feeds_into: 'KVAL  skupina C'</t>
         </is>
       </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="6" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" s="7" t="inlineStr">
+        <is>
+          <t>torzo</t>
+        </is>
+      </c>
+      <c r="C39" s="6" t="inlineStr">
+        <is>
+          <t>KVAL  skupina C (celostátní) · NODE_S2012_13_0032</t>
+        </is>
+      </c>
+      <c r="D39" s="6" t="inlineStr">
+        <is>
+          <t>máme jen účastníky (HC Orlová (MS)), chybí výsledek / odveta  [torzo-audit]</t>
+        </is>
+      </c>
+      <c r="E39" s="6" t="inlineStr">
+        <is>
+          <t>ne</t>
+        </is>
+      </c>
+      <c r="F39" s="6" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="6" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" s="7" t="inlineStr">
+        <is>
+          <t>torzo</t>
+        </is>
+      </c>
+      <c r="C40" s="6" t="inlineStr">
+        <is>
+          <t>30_Plzeňský L40 Finále (Plzeňský kraj) · NODE_S2012_13_0069</t>
+        </is>
+      </c>
+      <c r="D40" s="6" t="inlineStr">
+        <is>
+          <t>máme jen účastníky (SK Ježovy ,HC Gladiators ,HC Myslinka ,HC Dolní Kamenice a), chybí výsledek / odveta  [torzo-audit]</t>
+        </is>
+      </c>
+      <c r="E40" s="6" t="inlineStr">
+        <is>
+          <t>ne</t>
+        </is>
+      </c>
+      <c r="F40" s="6" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="6" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" s="7" t="inlineStr">
+        <is>
+          <t>torzo</t>
+        </is>
+      </c>
+      <c r="C41" s="6" t="inlineStr">
+        <is>
+          <t>30_Ústecký-Karlovarský L40 Finále · NODE_S2012_13_0073</t>
+        </is>
+      </c>
+      <c r="D41" s="6" t="inlineStr">
+        <is>
+          <t>máme jen účastníky (HC Rebel město Najdek loni jako HC Rebel Ostrov), chybí výsledek / odveta  [torzo-audit]</t>
+        </is>
+      </c>
+      <c r="E41" s="6" t="inlineStr">
+        <is>
+          <t>ne</t>
+        </is>
+      </c>
+      <c r="F41" s="6" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="6" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" s="7" t="inlineStr">
+        <is>
+          <t>torzo</t>
+        </is>
+      </c>
+      <c r="C42" s="6" t="inlineStr">
+        <is>
+          <t>30_Severomoravský L40 Finále (jihozápadní Morava) · NODE_S2012_13_0100</t>
+        </is>
+      </c>
+      <c r="D42" s="6" t="inlineStr">
+        <is>
+          <t>máme jen účastníky (HC Uničov z Olomouckého kraje, HC Rožnov pod Radhoštěm ze Zlínského kraje), chybí výsledek / odveta  [torzo-audit]</t>
+        </is>
+      </c>
+      <c r="E42" s="6" t="inlineStr">
+        <is>
+          <t>ne</t>
+        </is>
+      </c>
+      <c r="F42" s="6" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="6" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" s="7" t="inlineStr">
+        <is>
+          <t>torzo</t>
+        </is>
+      </c>
+      <c r="C43" s="6" t="inlineStr">
+        <is>
+          <t>Praha – Pražský přebor · NODE_S2012_13_0101</t>
+        </is>
+      </c>
+      <c r="D43" s="6" t="inlineStr">
+        <is>
+          <t>máme jen 2 týmy (HC Roudnice nad Labem, SK Černošice Tygři), chybí zbytek týmů a tabulka  [torzo-audit]</t>
+        </is>
+      </c>
+      <c r="E43" s="6" t="inlineStr">
+        <is>
+          <t>ne</t>
+        </is>
+      </c>
+      <c r="F43" s="6" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="6" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" s="7" t="inlineStr">
+        <is>
+          <t>torzo</t>
+        </is>
+      </c>
+      <c r="C44" s="6" t="inlineStr">
+        <is>
+          <t>Pardubický – Krajská liga · NODE_S2012_13_0103</t>
+        </is>
+      </c>
+      <c r="D44" s="6" t="inlineStr">
+        <is>
+          <t>máme jen 1 tým (HC Světlá nad Sázavou), chybí zbytek týmů i celá tabulka  [torzo-audit]</t>
+        </is>
+      </c>
+      <c r="E44" s="6" t="inlineStr">
+        <is>
+          <t>ne</t>
+        </is>
+      </c>
+      <c r="F44" s="6" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:F38"/>

--- a/data/S2012_13_FINAL.xlsx
+++ b/data/S2012_13_FINAL.xlsx
@@ -105,7 +105,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -118,6 +118,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -15308,7 +15311,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E44"/>
+  <dimension ref="A1:E50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15934,6 +15937,108 @@
         </is>
       </c>
       <c r="D44" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>NODE_S2012_13_0032</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>[TBD] torzo: máme jen účastníky (HC Orlová (MS)), chybí výsledek / odveta  [torzo-audit]</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>NODE_S2012_13_0069</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>[TBD] torzo: máme jen účastníky (SK Ježovy ,HC Gladiators ,HC Myslinka ,HC Dolní Kamenice a), chybí výsledek / odveta  [torzo-audit]</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>NODE_S2012_13_0073</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>[TBD] torzo: máme jen účastníky (HC Rebel město Najdek loni jako HC Rebel Ostrov), chybí výsledek / odveta  [torzo-audit]</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>NODE_S2012_13_0100</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>[TBD] torzo: máme jen účastníky (HC Uničov z Olomouckého kraje, HC Rožnov pod Radhoštěm ze Zlínského kraje), chybí výsledek / odveta  [torzo-audit]</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>NODE_S2012_13_0101</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>[TBD] torzo: máme jen 2 týmy (HC Roudnice nad Labem, SK Černošice Tygři), chybí zbytek týmů a tabulka  [torzo-audit]</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>NODE_S2012_13_0103</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>[TBD] torzo: máme jen 1 tým (HC Světlá nad Sázavou), chybí zbytek týmů i celá tabulka  [torzo-audit]</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
         <is>
           <t>TODO-auto</t>
         </is>
@@ -39294,7 +39399,7 @@
           <t>KVAL  skupina C (celostátní) · NODE_S2012_13_0032</t>
         </is>
       </c>
-      <c r="D39" s="6" t="inlineStr">
+      <c r="D39" s="8" t="inlineStr">
         <is>
           <t>máme jen účastníky (HC Orlová (MS)), chybí výsledek / odveta  [torzo-audit]</t>
         </is>
@@ -39320,7 +39425,7 @@
           <t>30_Plzeňský L40 Finále (Plzeňský kraj) · NODE_S2012_13_0069</t>
         </is>
       </c>
-      <c r="D40" s="6" t="inlineStr">
+      <c r="D40" s="8" t="inlineStr">
         <is>
           <t>máme jen účastníky (SK Ježovy ,HC Gladiators ,HC Myslinka ,HC Dolní Kamenice a), chybí výsledek / odveta  [torzo-audit]</t>
         </is>
@@ -39346,7 +39451,7 @@
           <t>30_Ústecký-Karlovarský L40 Finále · NODE_S2012_13_0073</t>
         </is>
       </c>
-      <c r="D41" s="6" t="inlineStr">
+      <c r="D41" s="8" t="inlineStr">
         <is>
           <t>máme jen účastníky (HC Rebel město Najdek loni jako HC Rebel Ostrov), chybí výsledek / odveta  [torzo-audit]</t>
         </is>
@@ -39372,7 +39477,7 @@
           <t>30_Severomoravský L40 Finále (jihozápadní Morava) · NODE_S2012_13_0100</t>
         </is>
       </c>
-      <c r="D42" s="6" t="inlineStr">
+      <c r="D42" s="8" t="inlineStr">
         <is>
           <t>máme jen účastníky (HC Uničov z Olomouckého kraje, HC Rožnov pod Radhoštěm ze Zlínského kraje), chybí výsledek / odveta  [torzo-audit]</t>
         </is>
@@ -39398,7 +39503,7 @@
           <t>Praha – Pražský přebor · NODE_S2012_13_0101</t>
         </is>
       </c>
-      <c r="D43" s="6" t="inlineStr">
+      <c r="D43" s="8" t="inlineStr">
         <is>
           <t>máme jen 2 týmy (HC Roudnice nad Labem, SK Černošice Tygři), chybí zbytek týmů a tabulka  [torzo-audit]</t>
         </is>
@@ -39424,7 +39529,7 @@
           <t>Pardubický – Krajská liga · NODE_S2012_13_0103</t>
         </is>
       </c>
-      <c r="D44" s="6" t="inlineStr">
+      <c r="D44" s="8" t="inlineStr">
         <is>
           <t>máme jen 1 tým (HC Světlá nad Sázavou), chybí zbytek týmů i celá tabulka  [torzo-audit]</t>
         </is>

--- a/data/S2012_13_FINAL.xlsx
+++ b/data/S2012_13_FINAL.xlsx
@@ -17793,7 +17793,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>KVAL  skupina A</t>
+          <t>KVAL skupina A</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -17830,7 +17830,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>KVAL  skupina B</t>
+          <t>KVAL skupina B</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -17867,7 +17867,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>KVAL  skupina C</t>
+          <t>KVAL skupina C</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -17904,7 +17904,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>30_Praha L40</t>
+          <t>Praha, 4. úroveň</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -17951,7 +17951,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>30_Praha L50</t>
+          <t>Praha, 5. úroveň</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -17993,7 +17993,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>30_Praha L50</t>
+          <t>Praha, 5. úroveň</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -18035,7 +18035,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>30_Praha L40 základní část</t>
+          <t>Praha, 4. úroveň, základní část</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -18085,7 +18085,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>30_Praha L40 finálová skupina</t>
+          <t>Praha, 4. úroveň finálová skupina</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -18127,7 +18127,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>30_Praha L40 skupina o 5.-10.místo</t>
+          <t>Praha, 4. úroveň, skupina o 5.-10.místo</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -18796,7 +18796,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>30_Středočeský L40</t>
+          <t>Středočeský, 4. úroveň</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -18843,7 +18843,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>30_Středočeský L40 základní část</t>
+          <t>Středočeský, 4. úroveň, základní část</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -18903,7 +18903,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>30_Středočeský L40 Finále</t>
+          <t>Středočeský, 4. úroveň, Finále</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -18958,7 +18958,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>30_Středočeský L40 základní část</t>
+          <t>Středočeský, 4. úroveň, základní část</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -19018,7 +19018,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>30_Středočeský L40 finálová skupina</t>
+          <t>Středočeský, 4. úroveň finálová skupina</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -19060,7 +19060,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>30_Jihočeský L40</t>
+          <t>Jihočeský, 4. úroveň</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -19107,7 +19107,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>30_Jihočeský L40 základní část</t>
+          <t>Jihočeský, 4. úroveň, základní část</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -19167,7 +19167,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>30_Jihočeský L40 Finále</t>
+          <t>Jihočeský, 4. úroveň, Finále</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -19222,7 +19222,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>30_Plzeňský L40</t>
+          <t>Plzeňský, 4. úroveň</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -19269,7 +19269,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>30_Plzeňský L40 základní část</t>
+          <t>Plzeňský, 4. úroveň, základní část</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -19324,7 +19324,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>30_Plzeňský L40 Finále</t>
+          <t>Plzeňský, 4. úroveň, Finále</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -19374,7 +19374,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>30_Plzeňský L40 skupina A</t>
+          <t>Plzeňský, 4. úroveň, skupina A</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -19421,7 +19421,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>30_Plzeňský L40 Finále</t>
+          <t>Plzeňský, 4. úroveň, Finále</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -19471,7 +19471,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>30_Plzeňský L40 skupina B</t>
+          <t>Plzeňský, 4. úroveň, skupina B</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -19518,7 +19518,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>30_Plzeňský L40 Finále</t>
+          <t>Plzeňský, 4. úroveň, Finále</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -19568,7 +19568,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>30_Plzeňský L40 skupina C</t>
+          <t>Plzeňský, 4. úroveň, skupina C</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -19615,7 +19615,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>30_Plzeňský L40 Finále</t>
+          <t>Plzeňský, 4. úroveň, Finále</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -19665,7 +19665,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>30_Plzeňský L40 skupina D</t>
+          <t>Plzeňský, 4. úroveň, skupina D</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -19712,7 +19712,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>30_Plzeňský L40 Finále</t>
+          <t>Plzeňský, 4. úroveň, Finále</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -19762,7 +19762,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>30_Ústecký-Karlovarský L40</t>
+          <t>Ústecký-Karlovarský, 4. úroveň</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -19809,7 +19809,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>30_Ústecký-Karlovarský L40 základní část</t>
+          <t>Ústecký-Karlovarský, 4. úroveň, základní část</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -19864,7 +19864,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>30_Ústecký-Karlovarský L40 Finále</t>
+          <t>Ústecký-Karlovarský, 4. úroveň, Finále</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -19919,7 +19919,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>30_Ústecký-Karlovarský L40 Finále</t>
+          <t>Ústecký-Karlovarský, 4. úroveň, Finále</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -19974,7 +19974,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>30_Karlovarský L40</t>
+          <t>Karlovarský, 4. úroveň</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -20016,7 +20016,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>30_Liberecký L40</t>
+          <t>Liberecký, 4. úroveň</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -20063,7 +20063,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>30_Liberecký L40 základní část</t>
+          <t>Liberecký, 4. úroveň, základní část</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -20118,7 +20118,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>30_Liberecký L40 Finále</t>
+          <t>Liberecký, 4. úroveň, Finále</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -20168,7 +20168,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>30_Hradecký L40</t>
+          <t>Hradecký, 4. úroveň</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -20215,7 +20215,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>30_Hradecký L40 základní část</t>
+          <t>Hradecký, 4. úroveň, základní část</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -20275,7 +20275,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>30_Hradecký L40 skupina o 9.-13.místo</t>
+          <t>Hradecký, 4. úroveň, skupina o 9.-13.místo</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -20325,7 +20325,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>30_Hradecký L40 Finále</t>
+          <t>Hradecký, 4. úroveň, Finále</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -20375,7 +20375,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>30_Pardubický L40</t>
+          <t>Pardubický, 4. úroveň</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -20422,7 +20422,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>30_Pardubický L40 skupina západ</t>
+          <t>Pardubický, 4. úroveň, skupina západ</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -20464,7 +20464,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>30_Pardubický L40 skupina střed</t>
+          <t>Pardubický, 4. úroveň, skupina střed</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -20506,7 +20506,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>30_Pardubický L40 skupina Východ</t>
+          <t>Pardubický, 4. úroveň, skupina Východ</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -20548,7 +20548,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>30_Pardubický L40 skupina A2</t>
+          <t>Pardubický, 4. úroveň, skupina A2</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -20590,7 +20590,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>30_Pardubický L40 skupina B2</t>
+          <t>Pardubický, 4. úroveň, skupina B2</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -20632,7 +20632,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>30_Pardubický L40 skupina A3</t>
+          <t>Pardubický, 4. úroveň, skupina A3</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -20674,7 +20674,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>30_Pardubický L40 skupina B3</t>
+          <t>Pardubický, 4. úroveň, skupina B3</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -20716,7 +20716,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>30_Pardubický L40 Finále</t>
+          <t>Pardubický, 4. úroveň, Finále</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -20766,7 +20766,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>30_Pardubický L40 Finále</t>
+          <t>Pardubický, 4. úroveň, Finále</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -20816,7 +20816,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>30_Vysočina L40</t>
+          <t>Vysočina, 4. úroveň</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -20863,7 +20863,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>30_Jihomoravský L40</t>
+          <t>Jihomoravský, 4. úroveň</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -20910,7 +20910,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>30_Jihomoravský L40 Jihomoravský krajský přebor</t>
+          <t>Jihomoravský, 4. úroveň Jihomoravský krajský přebor</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -20952,7 +20952,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>30_Jihomoravský L40 základní část</t>
+          <t>Jihomoravský, 4. úroveň, základní část</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -21012,7 +21012,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>30_Jihomoravský L40 Finále</t>
+          <t>Jihomoravský, 4. úroveň, Finále</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -21062,7 +21062,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>30_Jihomoravský L40 Finále</t>
+          <t>Jihomoravský, 4. úroveň, Finále</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -21112,7 +21112,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>30_Severomoravský L40</t>
+          <t>Severomoravský, 4. úroveň</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -21159,7 +21159,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>30_Severomoravský L40 základní část</t>
+          <t>Severomoravský, 4. úroveň, základní část</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -21219,7 +21219,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>30_Severomoravský L40 Finále</t>
+          <t>Severomoravský, 4. úroveň, Finále</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -21266,6 +21266,8 @@
         <v>5</v>
       </c>
     </row>
+    <row r="102"/>
+    <row r="103"/>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
@@ -21298,7 +21300,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>I.ČNHL (12 CZ) + SNHL (12 SVK)</t>
+          <t>I.ČNHL (12 CZ) + SNHL (12 Slovensko)</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
@@ -21395,6 +21397,7 @@
         </is>
       </c>
     </row>
+    <row r="111"/>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>

--- a/data/S2012_13_FINAL.xlsx
+++ b/data/S2012_13_FINAL.xlsx
@@ -823,7 +823,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -901,7 +901,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1140,7 +1140,7 @@
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1296,7 +1296,7 @@
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -1374,7 +1374,7 @@
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>zanik</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
@@ -1452,7 +1452,7 @@
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
@@ -1608,7 +1608,7 @@
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
@@ -1764,7 +1764,7 @@
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
@@ -5215,7 +5215,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>reorganizace</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -5293,7 +5293,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -5371,7 +5371,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>reorganizace</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -5449,7 +5449,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>reorganizace</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -5527,7 +5527,7 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>reorganizace</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -5605,7 +5605,7 @@
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>reorganizace</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -5683,7 +5683,7 @@
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>reorganizace</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -5761,7 +5761,7 @@
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>reorganizace</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -5839,7 +5839,7 @@
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>reorganizace</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
@@ -5917,7 +5917,7 @@
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>reorganizace</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
@@ -5995,7 +5995,7 @@
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>reorganizace</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
@@ -6073,7 +6073,7 @@
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>reorganizace</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
@@ -6151,7 +6151,7 @@
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>reorganizace</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
@@ -21266,8 +21266,6 @@
         <v>5</v>
       </c>
     </row>
-    <row r="102"/>
-    <row r="103"/>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
@@ -21397,7 +21395,6 @@
         </is>
       </c>
     </row>
-    <row r="111"/>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
@@ -21856,7 +21853,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -21934,7 +21931,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -22012,7 +22009,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -22090,7 +22087,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -22168,7 +22165,7 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -22246,7 +22243,7 @@
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -22324,7 +22321,7 @@
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>postup</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -22402,7 +22399,7 @@
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -22480,7 +22477,7 @@
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
@@ -22558,7 +22555,7 @@
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
@@ -22636,7 +22633,7 @@
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
@@ -22714,7 +22711,7 @@
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>o udržení</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
@@ -22792,7 +22789,7 @@
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
@@ -22870,7 +22867,7 @@
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>sestup</t>
+          <t>o udržení</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
@@ -23731,7 +23728,7 @@
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>udržel se</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
@@ -23809,7 +23806,7 @@
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>udržel se</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
@@ -23965,7 +23962,7 @@
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>udržel se</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
@@ -44553,7 +44550,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>setrval?</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -44631,7 +44628,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>postup</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -44709,7 +44706,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -44792,7 +44789,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -44870,7 +44867,7 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>o umístění</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -44953,7 +44950,7 @@
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>postup</t>
+          <t>o umístění</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -45036,7 +45033,7 @@
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>o umístění</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -45114,7 +45111,7 @@
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>o umístění</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -45192,7 +45189,7 @@
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>o umístění</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
@@ -45275,7 +45272,7 @@
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>o umístění</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
@@ -46755,7 +46752,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>reorganizace</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -46833,7 +46830,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>reorganizace</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -46911,7 +46908,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>reorganizace</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -46989,7 +46986,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>reorganizace</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -47072,7 +47069,7 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>reorganizace</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -47150,7 +47147,7 @@
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>reorganizace</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -47228,7 +47225,7 @@
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>reorganizace</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -47306,7 +47303,7 @@
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>reorganizace</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -47384,7 +47381,7 @@
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>reorganizace</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
@@ -47462,7 +47459,7 @@
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>reorganizace</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
@@ -47540,7 +47537,7 @@
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>reorganizace</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
@@ -47618,7 +47615,7 @@
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>reorganizace</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
@@ -47691,7 +47688,7 @@
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>reorganizace</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
@@ -47769,7 +47766,7 @@
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>reorganizace</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
@@ -47847,7 +47844,7 @@
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>reorganizace</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
@@ -47925,7 +47922,7 @@
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>reorganizace</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
@@ -58963,7 +58960,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -59041,7 +59038,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>reorganizace</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -59124,7 +59121,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -59202,7 +59199,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>reorganizace</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -59280,7 +59277,7 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -59358,7 +59355,7 @@
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
